--- a/KAMCHATKA_32616346943.xlsx
+++ b/KAMCHATKA_32616346943.xlsx
@@ -48,7 +48,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -58,11 +58,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00305496"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -136,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -187,9 +182,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -706,25 +698,25 @@
         <v>107</v>
       </c>
       <c r="C6" s="6" t="n">
+        <v>107</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>11768995.54</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>-1176899.554</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>317869.75</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>10909965.736</v>
+      </c>
+      <c r="H6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>26640201.75</v>
-      </c>
       <c r="I6" s="7" t="n">
-        <v>26640201.75</v>
+        <v>10909965.736</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
@@ -768,25 +760,25 @@
         <v>315</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>208</v>
+        <v>315</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>40300432</v>
+        <v>52069427.54000001</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>-4030043.2</v>
+        <v>-5206942.754000001</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>2751154.45</v>
+        <v>3069024.2</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>39021543.25</v>
+        <v>49931508.986</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>26640201.75</v>
+        <v>0</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>65661745</v>
+        <v>49931508.986</v>
       </c>
     </row>
     <row r="9" ht="53" customHeight="1">
@@ -870,7 +862,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>65661745</v>
+        <v>49931508.986</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -1657,12 +1649,16 @@
           <t>автоматическое/ручное</t>
         </is>
       </c>
-      <c r="K3" s="19" t="n"/>
+      <c r="K3" s="7" t="n">
+        <v>477825.81</v>
+      </c>
       <c r="L3" s="15">
         <f>IF(K3="","",K3*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M3" s="6" t="n"/>
+      <c r="M3" s="6" t="n">
+        <v>420</v>
+      </c>
       <c r="N3" s="15">
         <f>IF(K3="","",L3*E3)</f>
         <v/>
@@ -1679,14 +1675,26 @@
         <f>IF(P3="","",P3/E3)</f>
         <v/>
       </c>
-      <c r="R3" s="5" t="inlineStr"/>
-      <c r="S3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Авангард</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U3" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-predokhranitelnyi/flantcevyi/avangard/17ls17nzh/dn200-300</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -1731,12 +1739,16 @@
           <t xml:space="preserve">Ручное </t>
         </is>
       </c>
-      <c r="K4" s="19" t="n"/>
+      <c r="K4" s="7" t="n">
+        <v>169700</v>
+      </c>
       <c r="L4" s="15">
         <f>IF(K4="","",K4*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M4" s="6" t="n"/>
+      <c r="M4" s="6" t="n">
+        <v>150</v>
+      </c>
       <c r="N4" s="15">
         <f>IF(K4="","",L4*E4)</f>
         <v/>
@@ -1753,14 +1765,26 @@
         <f>IF(P4="","",P4/E4)</f>
         <v/>
       </c>
-      <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру / ТехГидроМаш</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка по соседнему типоразмеру/аналогу (источ</t>
+        </is>
+      </c>
       <c r="T4" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U4" s="5" t="inlineStr"/>
+          <t>analog: 15нж65нж Ду200 (масштаб от Ду150) · не проверен</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/stalnoi/shturval/tekhgidromash/15nzh65nzh-12h18n9tl/dn150</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -1805,12 +1829,16 @@
           <t xml:space="preserve">Ручное </t>
         </is>
       </c>
-      <c r="K5" s="19" t="n"/>
+      <c r="K5" s="7" t="n">
+        <v>16371.18</v>
+      </c>
       <c r="L5" s="15">
         <f>IF(K5="","",K5*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M5" s="6" t="n"/>
+      <c r="M5" s="6" t="n">
+        <v>14</v>
+      </c>
       <c r="N5" s="15">
         <f>IF(K5="","",L5*E5)</f>
         <v/>
@@ -1827,14 +1855,26 @@
         <f>IF(P5="","",P5/E5)</f>
         <v/>
       </c>
-      <c r="R5" s="5" t="inlineStr"/>
-      <c r="S5" s="5" t="inlineStr"/>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд ТехГидроМаш</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T5" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U5" s="5" t="inlineStr"/>
+          <t>analog: корпус 12Х18Н9ТЛ вместо 12Х18Н10Т · не проверен</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/stalnoi/shturval/tekhgidromash/15nzh65nzh-12h18n9tl/dn50</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -1879,12 +1919,16 @@
           <t xml:space="preserve">ручное </t>
         </is>
       </c>
-      <c r="K6" s="19" t="n"/>
+      <c r="K6" s="7" t="n">
+        <v>11000</v>
+      </c>
       <c r="L6" s="15">
         <f>IF(K6="","",K6*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M6" s="6" t="n"/>
+      <c r="M6" s="6" t="n">
+        <v>7.5</v>
+      </c>
       <c r="N6" s="15">
         <f>IF(K6="","",L6*E6)</f>
         <v/>
@@ -1901,14 +1945,26 @@
         <f>IF(P6="","",P6/E6)</f>
         <v/>
       </c>
-      <c r="R6" s="5" t="inlineStr"/>
-      <c r="S6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>АТКА через ВсеИнструменты</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка по соседнему типоразмеру/аналогу (источ</t>
+        </is>
+      </c>
       <c r="T6" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U6" s="5" t="inlineStr"/>
+          <t>exact (марка), цена оценочная · не проверено</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.vseinstrumenti.ru/product/klapan-ventil-zapornyj-atka-15s52nzh11-du40-ru63-pod-privarku-1005021205-13916407/</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -4209,12 +4265,16 @@
           <t>электропривод</t>
         </is>
       </c>
-      <c r="K32" s="19" t="n"/>
+      <c r="K32" s="7" t="n">
+        <v>101097.74</v>
+      </c>
       <c r="L32" s="15">
         <f>IF(K32="","",K32*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M32" s="6" t="n"/>
+      <c r="M32" s="6" t="n">
+        <v>26</v>
+      </c>
       <c r="N32" s="15">
         <f>IF(K32="","",L32*E32)</f>
         <v/>
@@ -4231,14 +4291,26 @@
         <f>IF(P32="","",P32/E32)</f>
         <v/>
       </c>
-      <c r="R32" s="5" t="inlineStr"/>
-      <c r="S32" s="5" t="inlineStr"/>
+      <c r="R32" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Авангард</t>
+        </is>
+      </c>
+      <c r="S32" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T32" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U32" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U32" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-reguliruiushchii/2hod/avangard/25s947nzh-ru25/dn50</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
@@ -4283,12 +4355,16 @@
           <t>автоматический</t>
         </is>
       </c>
-      <c r="K33" s="19" t="n"/>
+      <c r="K33" s="7" t="n">
+        <v>69709.58</v>
+      </c>
       <c r="L33" s="15">
         <f>IF(K33="","",K33*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M33" s="6" t="n"/>
+      <c r="M33" s="6" t="n">
+        <v>9</v>
+      </c>
       <c r="N33" s="15">
         <f>IF(K33="","",L33*E33)</f>
         <v/>
@@ -4305,14 +4381,26 @@
         <f>IF(P33="","",P33/E33)</f>
         <v/>
       </c>
-      <c r="R33" s="5" t="inlineStr"/>
-      <c r="S33" s="5" t="inlineStr"/>
+      <c r="R33" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Теплосила</t>
+        </is>
+      </c>
+      <c r="S33" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T33" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U33" s="5" t="inlineStr"/>
+          <t>analog: Теплосила TRV (25ч945п) + электропривод TSL 230</t>
+        </is>
+      </c>
+      <c r="U33" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-reguliruiushchii/2hod/teplosila/trv-tsl/dn15</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -4357,12 +4445,16 @@
           <t>автоматический</t>
         </is>
       </c>
-      <c r="K34" s="19" t="n"/>
+      <c r="K34" s="7" t="n">
+        <v>76636.74000000001</v>
+      </c>
       <c r="L34" s="15">
         <f>IF(K34="","",K34*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M34" s="6" t="n"/>
+      <c r="M34" s="6" t="n">
+        <v>13</v>
+      </c>
       <c r="N34" s="15">
         <f>IF(K34="","",L34*E34)</f>
         <v/>
@@ -4379,14 +4471,26 @@
         <f>IF(P34="","",P34/E34)</f>
         <v/>
       </c>
-      <c r="R34" s="5" t="inlineStr"/>
-      <c r="S34" s="5" t="inlineStr"/>
+      <c r="R34" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Теплосила</t>
+        </is>
+      </c>
+      <c r="S34" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T34" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U34" s="5" t="inlineStr"/>
+          <t>analog: Теплосила TRV (25ч945п) + электропривод TSL 230</t>
+        </is>
+      </c>
+      <c r="U34" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-reguliruiushchii/2hod/teplosila/trv-tsl/dn25</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="34" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
@@ -4431,12 +4535,16 @@
           <t>автоматический</t>
         </is>
       </c>
-      <c r="K35" s="19" t="n"/>
+      <c r="K35" s="7" t="n">
+        <v>94264.52</v>
+      </c>
       <c r="L35" s="15">
         <f>IF(K35="","",K35*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M35" s="6" t="n"/>
+      <c r="M35" s="6" t="n">
+        <v>26</v>
+      </c>
       <c r="N35" s="15">
         <f>IF(K35="","",L35*E35)</f>
         <v/>
@@ -4453,14 +4561,26 @@
         <f>IF(P35="","",P35/E35)</f>
         <v/>
       </c>
-      <c r="R35" s="5" t="inlineStr"/>
-      <c r="S35" s="5" t="inlineStr"/>
+      <c r="R35" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Теплосила</t>
+        </is>
+      </c>
+      <c r="S35" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T35" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U35" s="5" t="inlineStr"/>
+          <t>analog: Теплосила TRV (25ч945п) + электропривод TSL 230</t>
+        </is>
+      </c>
+      <c r="U35" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-reguliruiushchii/2hod/teplosila/trv-tsl/dn50</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
@@ -4505,12 +4625,16 @@
           <t>автоматический</t>
         </is>
       </c>
-      <c r="K36" s="19" t="n"/>
+      <c r="K36" s="7" t="n">
+        <v>159871.24</v>
+      </c>
       <c r="L36" s="15">
         <f>IF(K36="","",K36*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M36" s="6" t="n"/>
+      <c r="M36" s="6" t="n">
+        <v>45</v>
+      </c>
       <c r="N36" s="15">
         <f>IF(K36="","",L36*E36)</f>
         <v/>
@@ -4527,14 +4651,26 @@
         <f>IF(P36="","",P36/E36)</f>
         <v/>
       </c>
-      <c r="R36" s="5" t="inlineStr"/>
-      <c r="S36" s="5" t="inlineStr"/>
+      <c r="R36" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Теплосила</t>
+        </is>
+      </c>
+      <c r="S36" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T36" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U36" s="5" t="inlineStr"/>
+          <t>analog: Теплосила TRV Ду80 + привод TSL-2200 (24В, анал</t>
+        </is>
+      </c>
+      <c r="U36" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-reguliruiushchii/2hod/teplosila/trv-tsl-4-20ma-24v/dn80</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="34" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
@@ -4575,12 +4711,16 @@
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr"/>
-      <c r="K37" s="19" t="n"/>
+      <c r="K37" s="7" t="n">
+        <v>334724.08</v>
+      </c>
       <c r="L37" s="15">
         <f>IF(K37="","",K37*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M37" s="6" t="n"/>
+      <c r="M37" s="6" t="n">
+        <v>60</v>
+      </c>
       <c r="N37" s="15">
         <f>IF(K37="","",L37*E37)</f>
         <v/>
@@ -4597,14 +4737,26 @@
         <f>IF(P37="","",P37/E37)</f>
         <v/>
       </c>
-      <c r="R37" s="5" t="inlineStr"/>
-      <c r="S37" s="5" t="inlineStr"/>
+      <c r="R37" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Ридан</t>
+        </is>
+      </c>
+      <c r="S37" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T37" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U37" s="5" t="inlineStr"/>
+          <t>analog: Ду100 Ру25 (Ру16 в каталоге нет, Ру25 перекрыва</t>
+        </is>
+      </c>
+      <c r="U37" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-reguliruiushchii/2hod/ridan/vfg-2r/dn100-125-m3-h</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="34" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
@@ -4645,12 +4797,16 @@
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr"/>
-      <c r="K38" s="19" t="n"/>
+      <c r="K38" s="7" t="n">
+        <v>206414.85</v>
+      </c>
       <c r="L38" s="15">
         <f>IF(K38="","",K38*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M38" s="6" t="n"/>
+      <c r="M38" s="6" t="n">
+        <v>16</v>
+      </c>
       <c r="N38" s="15">
         <f>IF(K38="","",L38*E38)</f>
         <v/>
@@ -4667,14 +4823,26 @@
         <f>IF(P38="","",P38/E38)</f>
         <v/>
       </c>
-      <c r="R38" s="5" t="inlineStr"/>
-      <c r="S38" s="5" t="inlineStr"/>
+      <c r="R38" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Ридан</t>
+        </is>
+      </c>
+      <c r="S38" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T38" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U38" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U38" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-reguliruiushchii/2hod/ridan/vfg-2r/dn32-16-m3-h</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="34" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
@@ -4715,12 +4883,16 @@
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr"/>
-      <c r="K39" s="19" t="n"/>
+      <c r="K39" s="7" t="n">
+        <v>226123.95</v>
+      </c>
       <c r="L39" s="15">
         <f>IF(K39="","",K39*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M39" s="6" t="n"/>
+      <c r="M39" s="6" t="n">
+        <v>45</v>
+      </c>
       <c r="N39" s="15">
         <f>IF(K39="","",L39*E39)</f>
         <v/>
@@ -4737,14 +4909,26 @@
         <f>IF(P39="","",P39/E39)</f>
         <v/>
       </c>
-      <c r="R39" s="5" t="inlineStr"/>
-      <c r="S39" s="5" t="inlineStr"/>
+      <c r="R39" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Ридан</t>
+        </is>
+      </c>
+      <c r="S39" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T39" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U39" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U39" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-reguliruiushchii/2hod/ridan/vfg-2r/dn80-80-m3-h</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="34" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
@@ -4789,12 +4973,16 @@
           <t>автоматически действующая труб</t>
         </is>
       </c>
-      <c r="K40" s="19" t="n"/>
+      <c r="K40" s="7" t="n">
+        <v>58471.55</v>
+      </c>
       <c r="L40" s="15">
         <f>IF(K40="","",K40*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M40" s="6" t="n"/>
+      <c r="M40" s="6" t="n">
+        <v>13</v>
+      </c>
       <c r="N40" s="15">
         <f>IF(K40="","",L40*E40)</f>
         <v/>
@@ -4811,14 +4999,26 @@
         <f>IF(P40="","",P40/E40)</f>
         <v/>
       </c>
-      <c r="R40" s="5" t="inlineStr"/>
-      <c r="S40" s="5" t="inlineStr"/>
+      <c r="R40" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Теплоконтроль</t>
+        </is>
+      </c>
+      <c r="S40" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T40" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U40" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U40" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/regulyator/reguliator-davleniia-posle-sebia/teplokontrol/rd-no-chugun/dn25</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="34" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
@@ -4863,12 +5063,16 @@
           <t>автоматический</t>
         </is>
       </c>
-      <c r="K41" s="19" t="n"/>
+      <c r="K41" s="7" t="n">
+        <v>54538.27</v>
+      </c>
       <c r="L41" s="15">
         <f>IF(K41="","",K41*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M41" s="6" t="n"/>
+      <c r="M41" s="6" t="n">
+        <v>16</v>
+      </c>
       <c r="N41" s="15">
         <f>IF(K41="","",L41*E41)</f>
         <v/>
@@ -4885,14 +5089,26 @@
         <f>IF(P41="","",P41/E41)</f>
         <v/>
       </c>
-      <c r="R41" s="5" t="inlineStr"/>
-      <c r="S41" s="5" t="inlineStr"/>
+      <c r="R41" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Теплоконтроль</t>
+        </is>
+      </c>
+      <c r="S41" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T41" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U41" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U41" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/regulyator/reguliator-davleniia-posle-sebia/teplokontrol/rd-no-chugun/dn32</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="34" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
@@ -4937,12 +5153,16 @@
           <t>автоматический</t>
         </is>
       </c>
-      <c r="K42" s="19" t="n"/>
+      <c r="K42" s="7" t="n">
+        <v>79717.24000000001</v>
+      </c>
       <c r="L42" s="15">
         <f>IF(K42="","",K42*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M42" s="6" t="n"/>
+      <c r="M42" s="6" t="n">
+        <v>26</v>
+      </c>
       <c r="N42" s="15">
         <f>IF(K42="","",L42*E42)</f>
         <v/>
@@ -4959,14 +5179,26 @@
         <f>IF(P42="","",P42/E42)</f>
         <v/>
       </c>
-      <c r="R42" s="5" t="inlineStr"/>
-      <c r="S42" s="5" t="inlineStr"/>
+      <c r="R42" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Теплоконтроль</t>
+        </is>
+      </c>
+      <c r="S42" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T42" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U42" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U42" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/regulyator/reguliator-davleniia-posle-sebia/teplokontrol/rd-no-chugun/dn50</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="34" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
@@ -5011,12 +5243,16 @@
           <t>автоматический</t>
         </is>
       </c>
-      <c r="K43" s="19" t="n"/>
+      <c r="K43" s="7" t="n">
+        <v>101011.12</v>
+      </c>
       <c r="L43" s="15">
         <f>IF(K43="","",K43*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M43" s="6" t="n"/>
+      <c r="M43" s="6" t="n">
+        <v>45</v>
+      </c>
       <c r="N43" s="15">
         <f>IF(K43="","",L43*E43)</f>
         <v/>
@@ -5033,14 +5269,26 @@
         <f>IF(P43="","",P43/E43)</f>
         <v/>
       </c>
-      <c r="R43" s="5" t="inlineStr"/>
-      <c r="S43" s="5" t="inlineStr"/>
+      <c r="R43" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Теплоконтроль</t>
+        </is>
+      </c>
+      <c r="S43" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T43" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U43" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U43" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/regulyator/reguliator-davleniia-posle-sebia/teplokontrol/rd-no-chugun/dn80</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="34" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
@@ -5177,12 +5425,16 @@
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr"/>
-      <c r="K45" s="19" t="n"/>
+      <c r="K45" s="7" t="n">
+        <v>19411.42</v>
+      </c>
       <c r="L45" s="15">
         <f>IF(K45="","",K45*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M45" s="6" t="n"/>
+      <c r="M45" s="6" t="n">
+        <v>22</v>
+      </c>
       <c r="N45" s="15">
         <f>IF(K45="","",L45*E45)</f>
         <v/>
@@ -5199,14 +5451,26 @@
         <f>IF(P45="","",P45/E45)</f>
         <v/>
       </c>
-      <c r="R45" s="5" t="inlineStr"/>
-      <c r="S45" s="5" t="inlineStr"/>
+      <c r="R45" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд МЗТА</t>
+        </is>
+      </c>
+      <c r="S45" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T45" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U45" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U45" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/flantcevyi/povorotnyi/mzta/19s53nzh/dn80</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="34" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
@@ -5247,12 +5511,16 @@
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="19" t="n"/>
+      <c r="K46" s="7" t="n">
+        <v>51476.68</v>
+      </c>
       <c r="L46" s="15">
         <f>IF(K46="","",K46*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M46" s="6" t="n"/>
+      <c r="M46" s="6" t="n">
+        <v>60</v>
+      </c>
       <c r="N46" s="15">
         <f>IF(K46="","",L46*E46)</f>
         <v/>
@@ -5269,14 +5537,26 @@
         <f>IF(P46="","",P46/E46)</f>
         <v/>
       </c>
-      <c r="R46" s="5" t="inlineStr"/>
-      <c r="S46" s="5" t="inlineStr"/>
+      <c r="R46" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд МЗТА</t>
+        </is>
+      </c>
+      <c r="S46" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T46" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U46" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U46" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/flantcevyi/povorotnyi/mzta/19s53nzh/dn150</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="34" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
@@ -5321,12 +5601,16 @@
           <t>автоматический</t>
         </is>
       </c>
-      <c r="K47" s="19" t="n"/>
+      <c r="K47" s="7" t="n">
+        <v>4596.35</v>
+      </c>
       <c r="L47" s="15">
         <f>IF(K47="","",K47*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M47" s="6" t="n"/>
+      <c r="M47" s="6" t="n">
+        <v>3.5</v>
+      </c>
       <c r="N47" s="15">
         <f>IF(K47="","",L47*E47)</f>
         <v/>
@@ -5343,14 +5627,26 @@
         <f>IF(P47="","",P47/E47)</f>
         <v/>
       </c>
-      <c r="R47" s="5" t="inlineStr"/>
-      <c r="S47" s="5" t="inlineStr"/>
+      <c r="R47" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Мегастрой</t>
+        </is>
+      </c>
+      <c r="S47" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T47" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U47" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U47" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/mezhflantcevyi/odnostvorchatyi/megastroy/19ch21br/dn100</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="34" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
@@ -5395,12 +5691,16 @@
           <t>автоматический</t>
         </is>
       </c>
-      <c r="K48" s="19" t="n"/>
+      <c r="K48" s="7" t="n">
+        <v>2280.79</v>
+      </c>
       <c r="L48" s="15">
         <f>IF(K48="","",K48*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M48" s="6" t="n"/>
+      <c r="M48" s="6" t="n">
+        <v>1.5</v>
+      </c>
       <c r="N48" s="15">
         <f>IF(K48="","",L48*E48)</f>
         <v/>
@@ -5417,14 +5717,26 @@
         <f>IF(P48="","",P48/E48)</f>
         <v/>
       </c>
-      <c r="R48" s="5" t="inlineStr"/>
-      <c r="S48" s="5" t="inlineStr"/>
+      <c r="R48" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Мегастрой</t>
+        </is>
+      </c>
+      <c r="S48" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T48" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U48" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U48" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/mezhflantcevyi/odnostvorchatyi/megastroy/19ch21br/dn50</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="34" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
@@ -5469,12 +5781,16 @@
           <t>автоматический</t>
         </is>
       </c>
-      <c r="K49" s="19" t="n"/>
+      <c r="K49" s="7" t="n">
+        <v>3351.34</v>
+      </c>
       <c r="L49" s="15">
         <f>IF(K49="","",K49*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M49" s="6" t="n"/>
+      <c r="M49" s="6" t="n">
+        <v>2.5</v>
+      </c>
       <c r="N49" s="15">
         <f>IF(K49="","",L49*E49)</f>
         <v/>
@@ -5491,14 +5807,26 @@
         <f>IF(P49="","",P49/E49)</f>
         <v/>
       </c>
-      <c r="R49" s="5" t="inlineStr"/>
-      <c r="S49" s="5" t="inlineStr"/>
+      <c r="R49" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Мегастрой</t>
+        </is>
+      </c>
+      <c r="S49" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T49" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U49" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U49" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/mezhflantcevyi/odnostvorchatyi/megastroy/19ch21br/dn80</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="34" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
@@ -5543,12 +5871,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K50" s="19" t="n"/>
+      <c r="K50" s="7" t="n">
+        <v>10936.08</v>
+      </c>
       <c r="L50" s="15">
         <f>IF(K50="","",K50*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M50" s="6" t="n"/>
+      <c r="M50" s="6" t="n">
+        <v>5</v>
+      </c>
       <c r="N50" s="15">
         <f>IF(K50="","",L50*E50)</f>
         <v/>
@@ -5565,14 +5897,26 @@
         <f>IF(P50="","",P50/E50)</f>
         <v/>
       </c>
-      <c r="R50" s="5" t="inlineStr"/>
-      <c r="S50" s="5" t="inlineStr"/>
+      <c r="R50" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд АДЛ Гранлок</t>
+        </is>
+      </c>
+      <c r="S50" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T50" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U50" s="5" t="inlineStr"/>
+          <t xml:space="preserve">analog: АДЛ Гранлок CV16 (двухстворчатый межфланцевый, </t>
+        </is>
+      </c>
+      <c r="U50" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/mezhflantcevyi/dvukhstvorchatyi/granlok/cv16/dn100</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="34" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
@@ -5617,12 +5961,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K51" s="19" t="n"/>
+      <c r="K51" s="7" t="n">
+        <v>29968.69</v>
+      </c>
       <c r="L51" s="15">
         <f>IF(K51="","",K51*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M51" s="6" t="n"/>
+      <c r="M51" s="6" t="n">
+        <v>16</v>
+      </c>
       <c r="N51" s="15">
         <f>IF(K51="","",L51*E51)</f>
         <v/>
@@ -5639,14 +5987,26 @@
         <f>IF(P51="","",P51/E51)</f>
         <v/>
       </c>
-      <c r="R51" s="5" t="inlineStr"/>
-      <c r="S51" s="5" t="inlineStr"/>
+      <c r="R51" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд АДЛ Гранлок</t>
+        </is>
+      </c>
+      <c r="S51" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T51" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U51" s="5" t="inlineStr"/>
+          <t xml:space="preserve">analog: АДЛ Гранлок CV16 (двухстворчатый межфланцевый, </t>
+        </is>
+      </c>
+      <c r="U51" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/mezhflantcevyi/dvukhstvorchatyi/granlok/cv16/dn200</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="34" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
@@ -5687,12 +6047,16 @@
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr"/>
-      <c r="K52" s="19" t="n"/>
+      <c r="K52" s="7" t="n">
+        <v>15063.34</v>
+      </c>
       <c r="L52" s="15">
         <f>IF(K52="","",K52*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M52" s="6" t="n"/>
+      <c r="M52" s="6" t="n">
+        <v>13</v>
+      </c>
       <c r="N52" s="15">
         <f>IF(K52="","",L52*E52)</f>
         <v/>
@@ -5709,14 +6073,26 @@
         <f>IF(P52="","",P52/E52)</f>
         <v/>
       </c>
-      <c r="R52" s="5" t="inlineStr"/>
-      <c r="S52" s="5" t="inlineStr"/>
+      <c r="R52" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд МЗТА</t>
+        </is>
+      </c>
+      <c r="S52" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T52" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U52" s="5" t="inlineStr"/>
+          <t>analog: МЗТА 19с53нж Ду50 Ру40 (поворотный фланцевый) ·</t>
+        </is>
+      </c>
+      <c r="U52" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/flantcevyi/povorotnyi/mzta/19s53nzh/dn50</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="34" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
@@ -5761,12 +6137,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K53" s="19" t="n"/>
+      <c r="K53" s="7" t="n">
+        <v>12109.11</v>
+      </c>
       <c r="L53" s="15">
         <f>IF(K53="","",K53*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M53" s="6" t="n"/>
+      <c r="M53" s="6" t="n">
+        <v>9</v>
+      </c>
       <c r="N53" s="15">
         <f>IF(K53="","",L53*E53)</f>
         <v/>
@@ -5783,14 +6163,26 @@
         <f>IF(P53="","",P53/E53)</f>
         <v/>
       </c>
-      <c r="R53" s="5" t="inlineStr"/>
-      <c r="S53" s="5" t="inlineStr"/>
+      <c r="R53" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд АДЛ Гранлок</t>
+        </is>
+      </c>
+      <c r="S53" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T53" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U53" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U53" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/mezhflantcevyi/dvukhstvorchatyi/granlok/cv16/dn150</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="34" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
@@ -5835,12 +6227,16 @@
           <t>Клапан 16нж10нж является автом</t>
         </is>
       </c>
-      <c r="K54" s="19" t="n"/>
+      <c r="K54" s="7" t="n">
+        <v>42016.8</v>
+      </c>
       <c r="L54" s="15">
         <f>IF(K54="","",K54*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M54" s="6" t="n"/>
+      <c r="M54" s="6" t="n">
+        <v>14</v>
+      </c>
       <c r="N54" s="15">
         <f>IF(K54="","",L54*E54)</f>
         <v/>
@@ -5857,14 +6253,26 @@
         <f>IF(P54="","",P54/E54)</f>
         <v/>
       </c>
-      <c r="R54" s="5" t="inlineStr"/>
-      <c r="S54" s="5" t="inlineStr"/>
+      <c r="R54" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Победа-30</t>
+        </is>
+      </c>
+      <c r="S54" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T54" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U54" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U54" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/flantcevyi/podemnyi/pobeda30/16nj10nj/dn50</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="34" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
@@ -5909,12 +6317,16 @@
           <t>Клапан 16нж10нж является автом</t>
         </is>
       </c>
-      <c r="K55" s="19" t="n"/>
+      <c r="K55" s="7" t="n">
+        <v>30012</v>
+      </c>
       <c r="L55" s="15">
         <f>IF(K55="","",K55*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M55" s="6" t="n"/>
+      <c r="M55" s="6" t="n">
+        <v>7.5</v>
+      </c>
       <c r="N55" s="15">
         <f>IF(K55="","",L55*E55)</f>
         <v/>
@@ -5931,14 +6343,26 @@
         <f>IF(P55="","",P55/E55)</f>
         <v/>
       </c>
-      <c r="R55" s="5" t="inlineStr"/>
-      <c r="S55" s="5" t="inlineStr"/>
+      <c r="R55" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Победа-30</t>
+        </is>
+      </c>
+      <c r="S55" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T55" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U55" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U55" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/flantcevyi/podemnyi/pobeda30/16nj10nj/dn32</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="34" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
@@ -5983,12 +6407,16 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="K56" s="19" t="n"/>
+      <c r="K56" s="7" t="n">
+        <v>7205.32</v>
+      </c>
       <c r="L56" s="15">
         <f>IF(K56="","",K56*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M56" s="6" t="n"/>
+      <c r="M56" s="6" t="n">
+        <v>30</v>
+      </c>
       <c r="N56" s="15">
         <f>IF(K56="","",L56*E56)</f>
         <v/>
@@ -6005,14 +6433,26 @@
         <f>IF(P56="","",P56/E56)</f>
         <v/>
       </c>
-      <c r="R56" s="5" t="inlineStr"/>
-      <c r="S56" s="5" t="inlineStr"/>
+      <c r="R56" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд луидор</t>
+        </is>
+      </c>
+      <c r="S56" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T56" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U56" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U56" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/flantcevyi/priemnye/luidor/16ch42r/du100</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="34" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
@@ -6057,12 +6497,16 @@
           <t>ручное</t>
         </is>
       </c>
-      <c r="K57" s="19" t="n"/>
+      <c r="K57" s="7" t="n">
+        <v>180072</v>
+      </c>
       <c r="L57" s="15">
         <f>IF(K57="","",K57*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M57" s="6" t="n"/>
+      <c r="M57" s="6" t="n">
+        <v>30</v>
+      </c>
       <c r="N57" s="15">
         <f>IF(K57="","",L57*E57)</f>
         <v/>
@@ -6079,14 +6523,26 @@
         <f>IF(P57="","",P57/E57)</f>
         <v/>
       </c>
-      <c r="R57" s="5" t="inlineStr"/>
-      <c r="S57" s="5" t="inlineStr"/>
+      <c r="R57" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Победа-30</t>
+        </is>
+      </c>
+      <c r="S57" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T57" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U57" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U57" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/flantcevyi/povorotnyi/pobeda30/19nj76nj/dn100</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="34" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
@@ -6131,12 +6587,16 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="K58" s="19" t="n"/>
+      <c r="K58" s="7" t="n">
+        <v>16748.16</v>
+      </c>
       <c r="L58" s="15">
         <f>IF(K58="","",K58*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M58" s="6" t="n"/>
+      <c r="M58" s="6" t="n">
+        <v>22</v>
+      </c>
       <c r="N58" s="15">
         <f>IF(K58="","",L58*E58)</f>
         <v/>
@@ -6153,14 +6613,26 @@
         <f>IF(P58="","",P58/E58)</f>
         <v/>
       </c>
-      <c r="R58" s="5" t="inlineStr"/>
-      <c r="S58" s="5" t="inlineStr"/>
+      <c r="R58" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд МЗТА</t>
+        </is>
+      </c>
+      <c r="S58" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T58" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U58" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U58" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/flantcevyi/povorotnyi/mzta/19s76nzh/dn80</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="34" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
@@ -6205,12 +6677,16 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="K59" s="19" t="n"/>
+      <c r="K59" s="7" t="n">
+        <v>21720.27</v>
+      </c>
       <c r="L59" s="15">
         <f>IF(K59="","",K59*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M59" s="6" t="n"/>
+      <c r="M59" s="6" t="n">
+        <v>30</v>
+      </c>
       <c r="N59" s="15">
         <f>IF(K59="","",L59*E59)</f>
         <v/>
@@ -6227,14 +6703,26 @@
         <f>IF(P59="","",P59/E59)</f>
         <v/>
       </c>
-      <c r="R59" s="5" t="inlineStr"/>
-      <c r="S59" s="5" t="inlineStr"/>
+      <c r="R59" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд МЗТА</t>
+        </is>
+      </c>
+      <c r="S59" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T59" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U59" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U59" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/flantcevyi/povorotnyi/mzta/19s76nzh/dn100</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="34" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
@@ -6279,12 +6767,16 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="K60" s="19" t="n"/>
+      <c r="K60" s="7" t="n">
+        <v>12705.69</v>
+      </c>
       <c r="L60" s="15">
         <f>IF(K60="","",K60*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M60" s="6" t="n"/>
+      <c r="M60" s="6" t="n">
+        <v>13</v>
+      </c>
       <c r="N60" s="15">
         <f>IF(K60="","",L60*E60)</f>
         <v/>
@@ -6301,14 +6793,26 @@
         <f>IF(P60="","",P60/E60)</f>
         <v/>
       </c>
-      <c r="R60" s="5" t="inlineStr"/>
-      <c r="S60" s="5" t="inlineStr"/>
+      <c r="R60" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд МЗТА</t>
+        </is>
+      </c>
+      <c r="S60" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T60" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U60" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U60" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/flantcevyi/povorotnyi/mzta/19s76nzh/dn50</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="34" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
@@ -6349,12 +6853,16 @@
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr"/>
-      <c r="K61" s="19" t="n"/>
+      <c r="K61" s="7" t="n">
+        <v>71182.73</v>
+      </c>
       <c r="L61" s="15">
         <f>IF(K61="","",K61*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M61" s="6" t="n"/>
+      <c r="M61" s="6" t="n">
+        <v>6</v>
+      </c>
       <c r="N61" s="15">
         <f>IF(K61="","",L61*E61)</f>
         <v/>
@@ -6371,14 +6879,26 @@
         <f>IF(P61="","",P61/E61)</f>
         <v/>
       </c>
-      <c r="R61" s="5" t="inlineStr"/>
-      <c r="S61" s="5" t="inlineStr"/>
+      <c r="R61" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Ридан</t>
+        </is>
+      </c>
+      <c r="S61" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T61" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U61" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U61" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/mezhflantcevyi/pruzhinnyi/ridan/nvd-802r/dn125</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="34" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
@@ -6419,12 +6939,16 @@
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr"/>
-      <c r="K62" s="19" t="n"/>
+      <c r="K62" s="7" t="n">
+        <v>97307.81</v>
+      </c>
       <c r="L62" s="15">
         <f>IF(K62="","",K62*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M62" s="6" t="n"/>
+      <c r="M62" s="6" t="n">
+        <v>8</v>
+      </c>
       <c r="N62" s="15">
         <f>IF(K62="","",L62*E62)</f>
         <v/>
@@ -6441,14 +6965,26 @@
         <f>IF(P62="","",P62/E62)</f>
         <v/>
       </c>
-      <c r="R62" s="5" t="inlineStr"/>
-      <c r="S62" s="5" t="inlineStr"/>
+      <c r="R62" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Ридан</t>
+        </is>
+      </c>
+      <c r="S62" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T62" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U62" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U62" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/mezhflantcevyi/pruzhinnyi/ridan/nvd-802r/dn150</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="34" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
@@ -6751,12 +7287,16 @@
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr"/>
-      <c r="K66" s="19" t="n"/>
+      <c r="K66" s="7" t="n">
+        <v>195004.8</v>
+      </c>
       <c r="L66" s="15">
         <f>IF(K66="","",K66*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M66" s="6" t="n"/>
+      <c r="M66" s="6" t="n">
+        <v>6</v>
+      </c>
       <c r="N66" s="15">
         <f>IF(K66="","",L66*E66)</f>
         <v/>
@@ -6773,14 +7313,26 @@
         <f>IF(P66="","",P66/E66)</f>
         <v/>
       </c>
-      <c r="R66" s="5" t="inlineStr"/>
-      <c r="S66" s="5" t="inlineStr"/>
+      <c r="R66" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Ридан</t>
+        </is>
+      </c>
+      <c r="S66" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T66" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U66" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U66" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/mezhflantcevyi/pruzhinnyi/ridan/nvd-812r/dn150</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="34" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
@@ -6823,12 +7375,16 @@
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr"/>
-      <c r="K67" s="19" t="n"/>
+      <c r="K67" s="7" t="n">
+        <v>100164.44</v>
+      </c>
       <c r="L67" s="15">
         <f>IF(K67="","",K67*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M67" s="6" t="n"/>
+      <c r="M67" s="6" t="n">
+        <v>18</v>
+      </c>
       <c r="N67" s="15">
         <f>IF(K67="","",L67*E67)</f>
         <v/>
@@ -6845,14 +7401,26 @@
         <f>IF(P67="","",P67/E67)</f>
         <v/>
       </c>
-      <c r="R67" s="5" t="inlineStr"/>
-      <c r="S67" s="5" t="inlineStr"/>
+      <c r="R67" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд АДЛ Прегран</t>
+        </is>
+      </c>
+      <c r="S67" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T67" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U67" s="5" t="inlineStr"/>
+          <t>analog: АДЛ Прегран КПП 496 Ду32x50 Ру16 вместо ARI-SAF</t>
+        </is>
+      </c>
+      <c r="U67" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-predokhranitelnyi/flantcevyi/pregran/kpp-496-01-16-on1/dn32-50</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="34" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
@@ -6895,12 +7463,16 @@
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr"/>
-      <c r="K68" s="19" t="n"/>
+      <c r="K68" s="7" t="n">
+        <v>81586.28</v>
+      </c>
       <c r="L68" s="15">
         <f>IF(K68="","",K68*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M68" s="6" t="n"/>
+      <c r="M68" s="6" t="n">
+        <v>13</v>
+      </c>
       <c r="N68" s="15">
         <f>IF(K68="","",L68*E68)</f>
         <v/>
@@ -6917,14 +7489,26 @@
         <f>IF(P68="","",P68/E68)</f>
         <v/>
       </c>
-      <c r="R68" s="5" t="inlineStr"/>
-      <c r="S68" s="5" t="inlineStr"/>
+      <c r="R68" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд АДЛ Прегран</t>
+        </is>
+      </c>
+      <c r="S68" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T68" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U68" s="5" t="inlineStr"/>
+          <t>analog: АДЛ Прегран КПП 496 Ду25x40 Ру16 вместо ARI-SAF</t>
+        </is>
+      </c>
+      <c r="U68" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-predokhranitelnyi/flantcevyi/pregran/kpp-496-01-16-on1/dn25-40</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="34" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
@@ -6967,12 +7551,16 @@
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr"/>
-      <c r="K69" s="19" t="n"/>
+      <c r="K69" s="7" t="n">
+        <v>81586.28</v>
+      </c>
       <c r="L69" s="15">
         <f>IF(K69="","",K69*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M69" s="6" t="n"/>
+      <c r="M69" s="6" t="n">
+        <v>13</v>
+      </c>
       <c r="N69" s="15">
         <f>IF(K69="","",L69*E69)</f>
         <v/>
@@ -6989,14 +7577,26 @@
         <f>IF(P69="","",P69/E69)</f>
         <v/>
       </c>
-      <c r="R69" s="5" t="inlineStr"/>
-      <c r="S69" s="5" t="inlineStr"/>
+      <c r="R69" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд АДЛ Прегран</t>
+        </is>
+      </c>
+      <c r="S69" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T69" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U69" s="5" t="inlineStr"/>
+          <t>analog: АДЛ Прегран КПП 496 Ду25x40 Ру16 вместо ARI-SAF</t>
+        </is>
+      </c>
+      <c r="U69" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-predokhranitelnyi/flantcevyi/pregran/kpp-496-01-16-on1/dn25-40</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="34" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
@@ -7129,12 +7729,16 @@
           <t>Ручной</t>
         </is>
       </c>
-      <c r="K71" s="19" t="n"/>
+      <c r="K71" s="7" t="n">
+        <v>4500</v>
+      </c>
       <c r="L71" s="15">
         <f>IF(K71="","",K71*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M71" s="6" t="n"/>
+      <c r="M71" s="6" t="n">
+        <v>1.2</v>
+      </c>
       <c r="N71" s="15">
         <f>IF(K71="","",L71*E71)</f>
         <v/>
@@ -7151,11 +7755,19 @@
         <f>IF(P71="","",P71/E71)</f>
         <v/>
       </c>
-      <c r="R71" s="5" t="inlineStr"/>
-      <c r="S71" s="5" t="inlineStr"/>
+      <c r="R71" s="5" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+      <c r="S71" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка, без прямого прайса</t>
+        </is>
+      </c>
       <c r="T71" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
+          <t>exact (марка 22б16п/15б34бк1), цена оценочная · не пров</t>
         </is>
       </c>
       <c r="U71" s="5" t="inlineStr"/>
@@ -7203,12 +7815,16 @@
           <t xml:space="preserve">Ручное </t>
         </is>
       </c>
-      <c r="K72" s="19" t="n"/>
+      <c r="K72" s="7" t="n">
+        <v>26000</v>
+      </c>
       <c r="L72" s="15">
         <f>IF(K72="","",K72*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M72" s="6" t="n"/>
+      <c r="M72" s="6" t="n">
+        <v>27</v>
+      </c>
       <c r="N72" s="15">
         <f>IF(K72="","",L72*E72)</f>
         <v/>
@@ -7225,11 +7841,19 @@
         <f>IF(P72="","",P72/E72)</f>
         <v/>
       </c>
-      <c r="R72" s="5" t="inlineStr"/>
-      <c r="S72" s="5" t="inlineStr"/>
+      <c r="R72" s="5" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+      <c r="S72" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка, без прямого прайса</t>
+        </is>
+      </c>
       <c r="T72" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
+          <t>exact (ВДХ), цена оценочная · не проверено</t>
         </is>
       </c>
       <c r="U72" s="5" t="inlineStr"/>
@@ -7277,12 +7901,16 @@
           <t xml:space="preserve">Ручное </t>
         </is>
       </c>
-      <c r="K73" s="19" t="n"/>
+      <c r="K73" s="7" t="n">
+        <v>70000</v>
+      </c>
       <c r="L73" s="15">
         <f>IF(K73="","",K73*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M73" s="6" t="n"/>
+      <c r="M73" s="6" t="n">
+        <v>85</v>
+      </c>
       <c r="N73" s="15">
         <f>IF(K73="","",L73*E73)</f>
         <v/>
@@ -7299,11 +7927,19 @@
         <f>IF(P73="","",P73/E73)</f>
         <v/>
       </c>
-      <c r="R73" s="5" t="inlineStr"/>
-      <c r="S73" s="5" t="inlineStr"/>
+      <c r="R73" s="5" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+      <c r="S73" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка, без прямого прайса</t>
+        </is>
+      </c>
       <c r="T73" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
+          <t>exact (ВДХ), цена оценочная · не проверено</t>
         </is>
       </c>
       <c r="U73" s="5" t="inlineStr"/>
@@ -7351,12 +7987,16 @@
           <t xml:space="preserve">Ручное </t>
         </is>
       </c>
-      <c r="K74" s="19" t="n"/>
+      <c r="K74" s="7" t="n">
+        <v>16000</v>
+      </c>
       <c r="L74" s="15">
         <f>IF(K74="","",K74*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M74" s="6" t="n"/>
+      <c r="M74" s="6" t="n">
+        <v>14</v>
+      </c>
       <c r="N74" s="15">
         <f>IF(K74="","",L74*E74)</f>
         <v/>
@@ -7373,11 +8013,19 @@
         <f>IF(P74="","",P74/E74)</f>
         <v/>
       </c>
-      <c r="R74" s="5" t="inlineStr"/>
-      <c r="S74" s="5" t="inlineStr"/>
+      <c r="R74" s="5" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+      <c r="S74" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка, без прямого прайса</t>
+        </is>
+      </c>
       <c r="T74" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
+          <t>exact (ВДХ), цена оценочная · не проверено</t>
         </is>
       </c>
       <c r="U74" s="5" t="inlineStr"/>
@@ -7425,12 +8073,16 @@
           <t xml:space="preserve">Ручное </t>
         </is>
       </c>
-      <c r="K75" s="19" t="n"/>
+      <c r="K75" s="7" t="n">
+        <v>26000</v>
+      </c>
       <c r="L75" s="15">
         <f>IF(K75="","",K75*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M75" s="6" t="n"/>
+      <c r="M75" s="6" t="n">
+        <v>27</v>
+      </c>
       <c r="N75" s="15">
         <f>IF(K75="","",L75*E75)</f>
         <v/>
@@ -7447,11 +8099,19 @@
         <f>IF(P75="","",P75/E75)</f>
         <v/>
       </c>
-      <c r="R75" s="5" t="inlineStr"/>
-      <c r="S75" s="5" t="inlineStr"/>
+      <c r="R75" s="5" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+      <c r="S75" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка, без прямого прайса</t>
+        </is>
+      </c>
       <c r="T75" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
+          <t>exact (ВДХ), цена оценочная · не проверено</t>
         </is>
       </c>
       <c r="U75" s="5" t="inlineStr"/>
@@ -7499,12 +8159,16 @@
           <t>Ручной</t>
         </is>
       </c>
-      <c r="K76" s="19" t="n"/>
+      <c r="K76" s="7" t="n">
+        <v>3500</v>
+      </c>
       <c r="L76" s="15">
         <f>IF(K76="","",K76*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M76" s="6" t="n"/>
+      <c r="M76" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="N76" s="15">
         <f>IF(K76="","",L76*E76)</f>
         <v/>
@@ -7521,11 +8185,19 @@
         <f>IF(P76="","",P76/E76)</f>
         <v/>
       </c>
-      <c r="R76" s="5" t="inlineStr"/>
-      <c r="S76" s="5" t="inlineStr"/>
+      <c r="R76" s="5" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+      <c r="S76" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка, без прямого прайса</t>
+        </is>
+      </c>
       <c r="T76" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
+          <t>exact (марка), цена оценочная · не проверено</t>
         </is>
       </c>
       <c r="U76" s="5" t="inlineStr"/>
@@ -7573,12 +8245,16 @@
           <t>Ручной</t>
         </is>
       </c>
-      <c r="K77" s="19" t="n"/>
+      <c r="K77" s="7" t="n">
+        <v>5500</v>
+      </c>
       <c r="L77" s="15">
         <f>IF(K77="","",K77*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M77" s="6" t="n"/>
+      <c r="M77" s="6" t="n">
+        <v>5</v>
+      </c>
       <c r="N77" s="15">
         <f>IF(K77="","",L77*E77)</f>
         <v/>
@@ -7595,11 +8271,19 @@
         <f>IF(P77="","",P77/E77)</f>
         <v/>
       </c>
-      <c r="R77" s="5" t="inlineStr"/>
-      <c r="S77" s="5" t="inlineStr"/>
+      <c r="R77" s="5" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+      <c r="S77" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка, без прямого прайса</t>
+        </is>
+      </c>
       <c r="T77" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
+          <t>exact (марка), цена оценочная · не проверено</t>
         </is>
       </c>
       <c r="U77" s="5" t="inlineStr"/>
@@ -7647,12 +8331,16 @@
           <t>Ручной</t>
         </is>
       </c>
-      <c r="K78" s="19" t="n"/>
+      <c r="K78" s="7" t="n">
+        <v>8000</v>
+      </c>
       <c r="L78" s="15">
         <f>IF(K78="","",K78*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M78" s="6" t="n"/>
+      <c r="M78" s="6" t="n">
+        <v>7.5</v>
+      </c>
       <c r="N78" s="15">
         <f>IF(K78="","",L78*E78)</f>
         <v/>
@@ -7669,11 +8357,19 @@
         <f>IF(P78="","",P78/E78)</f>
         <v/>
       </c>
-      <c r="R78" s="5" t="inlineStr"/>
-      <c r="S78" s="5" t="inlineStr"/>
+      <c r="R78" s="5" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+      <c r="S78" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка, без прямого прайса</t>
+        </is>
+      </c>
       <c r="T78" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
+          <t>exact (марка), цена оценочная · не проверено</t>
         </is>
       </c>
       <c r="U78" s="5" t="inlineStr"/>
@@ -7721,12 +8417,16 @@
           <t>Ручной</t>
         </is>
       </c>
-      <c r="K79" s="19" t="n"/>
+      <c r="K79" s="7" t="n">
+        <v>496.54</v>
+      </c>
       <c r="L79" s="15">
         <f>IF(K79="","",K79*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M79" s="6" t="n"/>
+      <c r="M79" s="6" t="n">
+        <v>0.35</v>
+      </c>
       <c r="N79" s="15">
         <f>IF(K79="","",L79*E79)</f>
         <v/>
@@ -7743,14 +8443,26 @@
         <f>IF(P79="","",P79/E79)</f>
         <v/>
       </c>
-      <c r="R79" s="5" t="inlineStr"/>
-      <c r="S79" s="5" t="inlineStr"/>
+      <c r="R79" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Цветлит</t>
+        </is>
+      </c>
+      <c r="S79" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T79" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U79" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U79" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/latun/shturval/tsvetlit/15b1p/dn15</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="34" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
@@ -7795,12 +8507,16 @@
           <t>Ручной</t>
         </is>
       </c>
-      <c r="K80" s="19" t="n"/>
+      <c r="K80" s="7" t="n">
+        <v>653.3099999999999</v>
+      </c>
       <c r="L80" s="15">
         <f>IF(K80="","",K80*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M80" s="6" t="n"/>
+      <c r="M80" s="6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="N80" s="15">
         <f>IF(K80="","",L80*E80)</f>
         <v/>
@@ -7817,14 +8533,26 @@
         <f>IF(P80="","",P80/E80)</f>
         <v/>
       </c>
-      <c r="R80" s="5" t="inlineStr"/>
-      <c r="S80" s="5" t="inlineStr"/>
+      <c r="R80" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Цветлит</t>
+        </is>
+      </c>
+      <c r="S80" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T80" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U80" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U80" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/latun/shturval/tsvetlit/15b1p/dn20</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="34" customHeight="1">
       <c r="A81" s="5" t="inlineStr">
@@ -7869,12 +8597,16 @@
           <t>Ручной</t>
         </is>
       </c>
-      <c r="K81" s="19" t="n"/>
+      <c r="K81" s="7" t="n">
+        <v>923.54</v>
+      </c>
       <c r="L81" s="15">
         <f>IF(K81="","",K81*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M81" s="6" t="n"/>
+      <c r="M81" s="6" t="n">
+        <v>0.8</v>
+      </c>
       <c r="N81" s="15">
         <f>IF(K81="","",L81*E81)</f>
         <v/>
@@ -7891,14 +8623,26 @@
         <f>IF(P81="","",P81/E81)</f>
         <v/>
       </c>
-      <c r="R81" s="5" t="inlineStr"/>
-      <c r="S81" s="5" t="inlineStr"/>
+      <c r="R81" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Цветлит</t>
+        </is>
+      </c>
+      <c r="S81" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T81" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U81" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U81" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/latun/shturval/tsvetlit/15b1n-vr-vr/dn25</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="34" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
@@ -7943,12 +8687,16 @@
           <t>Ручной</t>
         </is>
       </c>
-      <c r="K82" s="19" t="n"/>
+      <c r="K82" s="7" t="n">
+        <v>1027.85</v>
+      </c>
       <c r="L82" s="15">
         <f>IF(K82="","",K82*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M82" s="6" t="n"/>
+      <c r="M82" s="6" t="n">
+        <v>1.2</v>
+      </c>
       <c r="N82" s="15">
         <f>IF(K82="","",L82*E82)</f>
         <v/>
@@ -7965,14 +8713,26 @@
         <f>IF(P82="","",P82/E82)</f>
         <v/>
       </c>
-      <c r="R82" s="5" t="inlineStr"/>
-      <c r="S82" s="5" t="inlineStr"/>
+      <c r="R82" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Цветлит</t>
+        </is>
+      </c>
+      <c r="S82" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T82" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U82" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U82" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/latun/shturval/tsvetlit/15b1p/dn32</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="34" customHeight="1">
       <c r="A83" s="5" t="inlineStr">
@@ -8017,12 +8777,16 @@
           <t>Ручной</t>
         </is>
       </c>
-      <c r="K83" s="19" t="n"/>
+      <c r="K83" s="7" t="n">
+        <v>1731.18</v>
+      </c>
       <c r="L83" s="15">
         <f>IF(K83="","",K83*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M83" s="6" t="n"/>
+      <c r="M83" s="6" t="n">
+        <v>1.8</v>
+      </c>
       <c r="N83" s="15">
         <f>IF(K83="","",L83*E83)</f>
         <v/>
@@ -8039,14 +8803,26 @@
         <f>IF(P83="","",P83/E83)</f>
         <v/>
       </c>
-      <c r="R83" s="5" t="inlineStr"/>
-      <c r="S83" s="5" t="inlineStr"/>
+      <c r="R83" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Цветлит</t>
+        </is>
+      </c>
+      <c r="S83" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T83" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U83" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U83" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/latun/shturval/tsvetlit/15b1p/dn40</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="34" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
@@ -8091,12 +8867,16 @@
           <t>Ручной</t>
         </is>
       </c>
-      <c r="K84" s="19" t="n"/>
+      <c r="K84" s="7" t="n">
+        <v>2197.83</v>
+      </c>
       <c r="L84" s="15">
         <f>IF(K84="","",K84*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M84" s="6" t="n"/>
+      <c r="M84" s="6" t="n">
+        <v>2.8</v>
+      </c>
       <c r="N84" s="15">
         <f>IF(K84="","",L84*E84)</f>
         <v/>
@@ -8113,14 +8893,26 @@
         <f>IF(P84="","",P84/E84)</f>
         <v/>
       </c>
-      <c r="R84" s="5" t="inlineStr"/>
-      <c r="S84" s="5" t="inlineStr"/>
+      <c r="R84" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Цветлит</t>
+        </is>
+      </c>
+      <c r="S84" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T84" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U84" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U84" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/latun/shturval/tsvetlit/15b1n-nr-vr/dn50</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="34" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
@@ -8165,12 +8957,16 @@
           <t>ручное</t>
         </is>
       </c>
-      <c r="K85" s="19" t="n"/>
+      <c r="K85" s="7" t="n">
+        <v>38136.59</v>
+      </c>
       <c r="L85" s="15">
         <f>IF(K85="","",K85*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M85" s="6" t="n"/>
+      <c r="M85" s="6" t="n">
+        <v>27</v>
+      </c>
       <c r="N85" s="15">
         <f>IF(K85="","",L85*E85)</f>
         <v/>
@@ -8187,14 +8983,26 @@
         <f>IF(P85="","",P85/E85)</f>
         <v/>
       </c>
-      <c r="R85" s="5" t="inlineStr"/>
-      <c r="S85" s="5" t="inlineStr"/>
+      <c r="R85" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд ТехГидроМаш</t>
+        </is>
+      </c>
+      <c r="S85" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T85" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U85" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U85" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/stalnoi/shturval/tekhgidromash/15nzh65nzh-12h18n9tl/dn80</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="34" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
@@ -8239,12 +9047,16 @@
           <t>ручное</t>
         </is>
       </c>
-      <c r="K86" s="19" t="n"/>
+      <c r="K86" s="7" t="n">
+        <v>43344.16</v>
+      </c>
       <c r="L86" s="15">
         <f>IF(K86="","",K86*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M86" s="6" t="n"/>
+      <c r="M86" s="6" t="n">
+        <v>40</v>
+      </c>
       <c r="N86" s="15">
         <f>IF(K86="","",L86*E86)</f>
         <v/>
@@ -8261,14 +9073,26 @@
         <f>IF(P86="","",P86/E86)</f>
         <v/>
       </c>
-      <c r="R86" s="5" t="inlineStr"/>
-      <c r="S86" s="5" t="inlineStr"/>
+      <c r="R86" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд ТехГидроМаш</t>
+        </is>
+      </c>
+      <c r="S86" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T86" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U86" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U86" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/stalnoi/shturval/tekhgidromash/15nzh65nzh-12h18n9tl/dn100</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="34" customHeight="1">
       <c r="A87" s="5" t="inlineStr">
@@ -8313,12 +9137,16 @@
           <t>ручное</t>
         </is>
       </c>
-      <c r="K87" s="19" t="n"/>
+      <c r="K87" s="7" t="n">
+        <v>77477.92999999999</v>
+      </c>
       <c r="L87" s="15">
         <f>IF(K87="","",K87*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M87" s="6" t="n"/>
+      <c r="M87" s="6" t="n">
+        <v>60</v>
+      </c>
       <c r="N87" s="15">
         <f>IF(K87="","",L87*E87)</f>
         <v/>
@@ -8335,14 +9163,26 @@
         <f>IF(P87="","",P87/E87)</f>
         <v/>
       </c>
-      <c r="R87" s="5" t="inlineStr"/>
-      <c r="S87" s="5" t="inlineStr"/>
+      <c r="R87" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд ТехГидроМаш</t>
+        </is>
+      </c>
+      <c r="S87" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T87" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U87" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U87" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/stalnoi/shturval/tekhgidromash/15nzh65nzh-12h18n9tl/dn125</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="34" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
@@ -8387,12 +9227,16 @@
           <t>ручное</t>
         </is>
       </c>
-      <c r="K88" s="19" t="n"/>
+      <c r="K88" s="7" t="n">
+        <v>102852.71</v>
+      </c>
       <c r="L88" s="15">
         <f>IF(K88="","",K88*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M88" s="6" t="n"/>
+      <c r="M88" s="6" t="n">
+        <v>85</v>
+      </c>
       <c r="N88" s="15">
         <f>IF(K88="","",L88*E88)</f>
         <v/>
@@ -8409,14 +9253,26 @@
         <f>IF(P88="","",P88/E88)</f>
         <v/>
       </c>
-      <c r="R88" s="5" t="inlineStr"/>
-      <c r="S88" s="5" t="inlineStr"/>
+      <c r="R88" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд ТехГидроМаш</t>
+        </is>
+      </c>
+      <c r="S88" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T88" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U88" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U88" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/stalnoi/shturval/tekhgidromash/15nzh65nzh-12h18n9tl/dn150</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="34" customHeight="1">
       <c r="A89" s="5" t="inlineStr">
@@ -8461,12 +9317,16 @@
           <t>ручное</t>
         </is>
       </c>
-      <c r="K89" s="19" t="n"/>
+      <c r="K89" s="7" t="n">
+        <v>11899.88</v>
+      </c>
       <c r="L89" s="15">
         <f>IF(K89="","",K89*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M89" s="6" t="n"/>
+      <c r="M89" s="6" t="n">
+        <v>7.5</v>
+      </c>
       <c r="N89" s="15">
         <f>IF(K89="","",L89*E89)</f>
         <v/>
@@ -8483,14 +9343,26 @@
         <f>IF(P89="","",P89/E89)</f>
         <v/>
       </c>
-      <c r="R89" s="5" t="inlineStr"/>
-      <c r="S89" s="5" t="inlineStr"/>
+      <c r="R89" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд ТехГидроМаш</t>
+        </is>
+      </c>
+      <c r="S89" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T89" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U89" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U89" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/stalnoi/shturval/tekhgidromash/15nzh65nzh-12h18n9tl/dn32</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="34" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
@@ -8535,12 +9407,16 @@
           <t>ручное</t>
         </is>
       </c>
-      <c r="K90" s="19" t="n"/>
+      <c r="K90" s="7" t="n">
+        <v>16371.18</v>
+      </c>
       <c r="L90" s="15">
         <f>IF(K90="","",K90*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M90" s="6" t="n"/>
+      <c r="M90" s="6" t="n">
+        <v>14</v>
+      </c>
       <c r="N90" s="15">
         <f>IF(K90="","",L90*E90)</f>
         <v/>
@@ -8557,14 +9433,26 @@
         <f>IF(P90="","",P90/E90)</f>
         <v/>
       </c>
-      <c r="R90" s="5" t="inlineStr"/>
-      <c r="S90" s="5" t="inlineStr"/>
+      <c r="R90" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд ТехГидроМаш</t>
+        </is>
+      </c>
+      <c r="S90" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T90" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U90" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U90" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/stalnoi/shturval/tekhgidromash/15nzh65nzh-12h18n9tl/dn50</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="34" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
@@ -8609,12 +9497,16 @@
           <t>ручное</t>
         </is>
       </c>
-      <c r="K91" s="19" t="n"/>
+      <c r="K91" s="7" t="n">
+        <v>7500</v>
+      </c>
       <c r="L91" s="15">
         <f>IF(K91="","",K91*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M91" s="6" t="n"/>
+      <c r="M91" s="6" t="n">
+        <v>7.5</v>
+      </c>
       <c r="N91" s="15">
         <f>IF(K91="","",L91*E91)</f>
         <v/>
@@ -8631,14 +9523,26 @@
         <f>IF(P91="","",P91/E91)</f>
         <v/>
       </c>
-      <c r="R91" s="5" t="inlineStr"/>
-      <c r="S91" s="5" t="inlineStr"/>
+      <c r="R91" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру, «Россия»</t>
+        </is>
+      </c>
+      <c r="S91" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка по соседнему типоразмеру/аналогу (источ</t>
+        </is>
+      </c>
       <c r="T91" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U91" s="5" t="inlineStr"/>
+          <t>exact (марка), оценка по соседнему Ду · не проверено</t>
+        </is>
+      </c>
+      <c r="U91" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/stalnoi/shturval/russia/15s22nzh/dn40</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="34" customHeight="1">
       <c r="A92" s="5" t="inlineStr">
@@ -8683,12 +9587,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K92" s="19" t="n"/>
+      <c r="K92" s="7" t="n">
+        <v>10529.82</v>
+      </c>
       <c r="L92" s="15">
         <f>IF(K92="","",K92*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M92" s="6" t="n"/>
+      <c r="M92" s="6" t="n">
+        <v>14</v>
+      </c>
       <c r="N92" s="15">
         <f>IF(K92="","",L92*E92)</f>
         <v/>
@@ -8705,14 +9613,26 @@
         <f>IF(P92="","",P92/E92)</f>
         <v/>
       </c>
-      <c r="R92" s="5" t="inlineStr"/>
-      <c r="S92" s="5" t="inlineStr"/>
+      <c r="R92" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Россия</t>
+        </is>
+      </c>
+      <c r="S92" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T92" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U92" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U92" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/stalnoi/shturval/russia/15s22nzh/dn50</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="34" customHeight="1">
       <c r="A93" s="5" t="inlineStr">
@@ -8757,12 +9677,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K93" s="19" t="n"/>
+      <c r="K93" s="7" t="n">
+        <v>19907.96</v>
+      </c>
       <c r="L93" s="15">
         <f>IF(K93="","",K93*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M93" s="6" t="n"/>
+      <c r="M93" s="6" t="n">
+        <v>27</v>
+      </c>
       <c r="N93" s="15">
         <f>IF(K93="","",L93*E93)</f>
         <v/>
@@ -8779,14 +9703,26 @@
         <f>IF(P93="","",P93/E93)</f>
         <v/>
       </c>
-      <c r="R93" s="5" t="inlineStr"/>
-      <c r="S93" s="5" t="inlineStr"/>
+      <c r="R93" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Россия</t>
+        </is>
+      </c>
+      <c r="S93" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T93" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U93" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U93" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/stalnoi/shturval/russia/15s22nzh/dn80</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="34" customHeight="1">
       <c r="A94" s="5" t="inlineStr">
@@ -8831,12 +9767,16 @@
           <t>ручное</t>
         </is>
       </c>
-      <c r="K94" s="19" t="n"/>
+      <c r="K94" s="7" t="n">
+        <v>8000</v>
+      </c>
       <c r="L94" s="15">
         <f>IF(K94="","",K94*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M94" s="6" t="n"/>
+      <c r="M94" s="6" t="n">
+        <v>4</v>
+      </c>
       <c r="N94" s="15">
         <f>IF(K94="","",L94*E94)</f>
         <v/>
@@ -8853,14 +9793,26 @@
         <f>IF(P94="","",P94/E94)</f>
         <v/>
       </c>
-      <c r="R94" s="5" t="inlineStr"/>
-      <c r="S94" s="5" t="inlineStr"/>
+      <c r="R94" s="5" t="inlineStr">
+        <is>
+          <t>АТКА</t>
+        </is>
+      </c>
+      <c r="S94" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка по соседнему типоразмеру/аналогу (источ</t>
+        </is>
+      </c>
       <c r="T94" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U94" s="5" t="inlineStr"/>
+          <t>exact (марка), цена оценочная · не проверено</t>
+        </is>
+      </c>
+      <c r="U94" s="5" t="inlineStr">
+        <is>
+          <t>https://www.vseinstrumenti.ru/product/klapan-ventil-zapornyj-atka-15s52nzh11-du40-ru63-pod-privarku-1005021205-13916407/</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="34" customHeight="1">
       <c r="A95" s="5" t="inlineStr">
@@ -8905,12 +9857,16 @@
           <t>ручное</t>
         </is>
       </c>
-      <c r="K95" s="19" t="n"/>
+      <c r="K95" s="7" t="n">
+        <v>4500</v>
+      </c>
       <c r="L95" s="15">
         <f>IF(K95="","",K95*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M95" s="6" t="n"/>
+      <c r="M95" s="6" t="n">
+        <v>5</v>
+      </c>
       <c r="N95" s="15">
         <f>IF(K95="","",L95*E95)</f>
         <v/>
@@ -8927,11 +9883,19 @@
         <f>IF(P95="","",P95/E95)</f>
         <v/>
       </c>
-      <c r="R95" s="5" t="inlineStr"/>
-      <c r="S95" s="5" t="inlineStr"/>
+      <c r="R95" s="5" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+      <c r="S95" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка, без прямого прайса</t>
+        </is>
+      </c>
       <c r="T95" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
+          <t>exact (марка), цена оценочная · не проверено</t>
         </is>
       </c>
       <c r="U95" s="5" t="inlineStr"/>
@@ -8979,12 +9943,16 @@
           <t>ручное</t>
         </is>
       </c>
-      <c r="K96" s="19" t="n"/>
+      <c r="K96" s="7" t="n">
+        <v>8000</v>
+      </c>
       <c r="L96" s="15">
         <f>IF(K96="","",K96*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M96" s="6" t="n"/>
+      <c r="M96" s="6" t="n">
+        <v>14</v>
+      </c>
       <c r="N96" s="15">
         <f>IF(K96="","",L96*E96)</f>
         <v/>
@@ -9001,11 +9969,19 @@
         <f>IF(P96="","",P96/E96)</f>
         <v/>
       </c>
-      <c r="R96" s="5" t="inlineStr"/>
-      <c r="S96" s="5" t="inlineStr"/>
+      <c r="R96" s="5" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+      <c r="S96" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка, без прямого прайса</t>
+        </is>
+      </c>
       <c r="T96" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
+          <t>exact (марка), цена оценочная · не проверено</t>
         </is>
       </c>
       <c r="U96" s="5" t="inlineStr"/>
@@ -9053,12 +10029,16 @@
           <t>ручное</t>
         </is>
       </c>
-      <c r="K97" s="19" t="n"/>
+      <c r="K97" s="7" t="n">
+        <v>12000</v>
+      </c>
       <c r="L97" s="15">
         <f>IF(K97="","",K97*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M97" s="6" t="n"/>
+      <c r="M97" s="6" t="n">
+        <v>27</v>
+      </c>
       <c r="N97" s="15">
         <f>IF(K97="","",L97*E97)</f>
         <v/>
@@ -9075,11 +10055,19 @@
         <f>IF(P97="","",P97/E97)</f>
         <v/>
       </c>
-      <c r="R97" s="5" t="inlineStr"/>
-      <c r="S97" s="5" t="inlineStr"/>
+      <c r="R97" s="5" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+      <c r="S97" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка, без прямого прайса</t>
+        </is>
+      </c>
       <c r="T97" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
+          <t>exact (марка), цена оценочная · не проверено</t>
         </is>
       </c>
       <c r="U97" s="5" t="inlineStr"/>
@@ -9127,12 +10115,16 @@
           <t>ручное</t>
         </is>
       </c>
-      <c r="K98" s="19" t="n"/>
+      <c r="K98" s="7" t="n">
+        <v>6000</v>
+      </c>
       <c r="L98" s="15">
         <f>IF(K98="","",K98*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M98" s="6" t="n"/>
+      <c r="M98" s="6" t="n">
+        <v>4</v>
+      </c>
       <c r="N98" s="15">
         <f>IF(K98="","",L98*E98)</f>
         <v/>
@@ -9149,11 +10141,19 @@
         <f>IF(P98="","",P98/E98)</f>
         <v/>
       </c>
-      <c r="R98" s="5" t="inlineStr"/>
-      <c r="S98" s="5" t="inlineStr"/>
+      <c r="R98" s="5" t="inlineStr">
+        <is>
+          <t>оценка</t>
+        </is>
+      </c>
+      <c r="S98" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка, без прямого прайса</t>
+        </is>
+      </c>
       <c r="T98" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
+          <t>exact (марка), цена оценочная · не проверено</t>
         </is>
       </c>
       <c r="U98" s="5" t="inlineStr"/>
@@ -17895,12 +18895,16 @@
           <t>Ручной</t>
         </is>
       </c>
-      <c r="K196" s="19" t="n"/>
+      <c r="K196" s="7" t="n">
+        <v>550</v>
+      </c>
       <c r="L196" s="15">
         <f>IF(K196="","",K196*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M196" s="6" t="n"/>
+      <c r="M196" s="6" t="n">
+        <v>1.3</v>
+      </c>
       <c r="N196" s="15">
         <f>IF(K196="","",L196*E196)</f>
         <v/>
@@ -17917,14 +18921,26 @@
         <f>IF(P196="","",P196/E196)</f>
         <v/>
       </c>
-      <c r="R196" s="5" t="inlineStr"/>
-      <c r="S196" s="5" t="inlineStr"/>
+      <c r="R196" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру</t>
+        </is>
+      </c>
+      <c r="S196" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка по соседнему типоразмеру/аналогу (источ</t>
+        </is>
+      </c>
       <c r="T196" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U196" s="5" t="inlineStr"/>
+          <t>exact (марка), оценка рос. исполнения · не проверено</t>
+        </is>
+      </c>
+      <c r="U196" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/chugun/shturval/kitai/15kch18p1/dn25</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="34" customHeight="1">
       <c r="A197" s="5" t="inlineStr">
@@ -19499,12 +20515,16 @@
           <t>электропривод ST «Regada»</t>
         </is>
       </c>
-      <c r="K214" s="19" t="n"/>
+      <c r="K214" s="7" t="n">
+        <v>81720.48</v>
+      </c>
       <c r="L214" s="15">
         <f>IF(K214="","",K214*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M214" s="6" t="n"/>
+      <c r="M214" s="6" t="n">
+        <v>13</v>
+      </c>
       <c r="N214" s="15">
         <f>IF(K214="","",L214*E214)</f>
         <v/>
@@ -19521,14 +20541,26 @@
         <f>IF(P214="","",P214/E214)</f>
         <v/>
       </c>
-      <c r="R214" s="5" t="inlineStr"/>
-      <c r="S214" s="5" t="inlineStr"/>
+      <c r="R214" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Авангард</t>
+        </is>
+      </c>
+      <c r="S214" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T214" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U214" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U214" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-reguliruiushchii/2hod/avangard/25s947nzh-ru25/dn25</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="34" customHeight="1">
       <c r="A215" s="5" t="inlineStr">
@@ -19573,12 +20605,16 @@
           <t>электропривод ST «Regada»</t>
         </is>
       </c>
-      <c r="K215" s="19" t="n"/>
+      <c r="K215" s="7" t="n">
+        <v>101097.74</v>
+      </c>
       <c r="L215" s="15">
         <f>IF(K215="","",K215*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M215" s="6" t="n"/>
+      <c r="M215" s="6" t="n">
+        <v>26</v>
+      </c>
       <c r="N215" s="15">
         <f>IF(K215="","",L215*E215)</f>
         <v/>
@@ -19595,14 +20631,26 @@
         <f>IF(P215="","",P215/E215)</f>
         <v/>
       </c>
-      <c r="R215" s="5" t="inlineStr"/>
-      <c r="S215" s="5" t="inlineStr"/>
+      <c r="R215" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Авангард</t>
+        </is>
+      </c>
+      <c r="S215" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T215" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U215" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U215" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-reguliruiushchii/2hod/avangard/25s947nzh-ru25/dn50</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="34" customHeight="1">
       <c r="A216" s="5" t="inlineStr">
@@ -19647,12 +20695,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K216" s="19" t="n"/>
+      <c r="K216" s="7" t="n">
+        <v>226123.95</v>
+      </c>
       <c r="L216" s="15">
         <f>IF(K216="","",K216*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M216" s="6" t="n"/>
+      <c r="M216" s="6" t="n">
+        <v>45</v>
+      </c>
       <c r="N216" s="15">
         <f>IF(K216="","",L216*E216)</f>
         <v/>
@@ -19669,14 +20721,26 @@
         <f>IF(P216="","",P216/E216)</f>
         <v/>
       </c>
-      <c r="R216" s="5" t="inlineStr"/>
-      <c r="S216" s="5" t="inlineStr"/>
+      <c r="R216" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Ридан</t>
+        </is>
+      </c>
+      <c r="S216" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T216" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U216" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U216" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-reguliruiushchii/2hod/ridan/vfg-2r/dn80-80-m3-h</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="34" customHeight="1">
       <c r="A217" s="5" t="inlineStr">
@@ -19721,12 +20785,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K217" s="19" t="n"/>
+      <c r="K217" s="7" t="n">
+        <v>4596.35</v>
+      </c>
       <c r="L217" s="15">
         <f>IF(K217="","",K217*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M217" s="6" t="n"/>
+      <c r="M217" s="6" t="n">
+        <v>3.5</v>
+      </c>
       <c r="N217" s="15">
         <f>IF(K217="","",L217*E217)</f>
         <v/>
@@ -19743,14 +20811,26 @@
         <f>IF(P217="","",P217/E217)</f>
         <v/>
       </c>
-      <c r="R217" s="5" t="inlineStr"/>
-      <c r="S217" s="5" t="inlineStr"/>
+      <c r="R217" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Мегастрой</t>
+        </is>
+      </c>
+      <c r="S217" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T217" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U217" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U217" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/mezhflantcevyi/odnostvorchatyi/megastroy/19ch21br/dn100</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="34" customHeight="1">
       <c r="A218" s="5" t="inlineStr">
@@ -19795,12 +20875,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K218" s="19" t="n"/>
+      <c r="K218" s="7" t="n">
+        <v>2280.79</v>
+      </c>
       <c r="L218" s="15">
         <f>IF(K218="","",K218*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M218" s="6" t="n"/>
+      <c r="M218" s="6" t="n">
+        <v>1.5</v>
+      </c>
       <c r="N218" s="15">
         <f>IF(K218="","",L218*E218)</f>
         <v/>
@@ -19817,14 +20901,26 @@
         <f>IF(P218="","",P218/E218)</f>
         <v/>
       </c>
-      <c r="R218" s="5" t="inlineStr"/>
-      <c r="S218" s="5" t="inlineStr"/>
+      <c r="R218" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Мегастрой</t>
+        </is>
+      </c>
+      <c r="S218" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T218" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U218" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U218" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/mezhflantcevyi/odnostvorchatyi/megastroy/19ch21br/dn50</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="34" customHeight="1">
       <c r="A219" s="5" t="inlineStr">
@@ -19869,12 +20965,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K219" s="19" t="n"/>
+      <c r="K219" s="7" t="n">
+        <v>3351.34</v>
+      </c>
       <c r="L219" s="15">
         <f>IF(K219="","",K219*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M219" s="6" t="n"/>
+      <c r="M219" s="6" t="n">
+        <v>2.5</v>
+      </c>
       <c r="N219" s="15">
         <f>IF(K219="","",L219*E219)</f>
         <v/>
@@ -19891,14 +20991,26 @@
         <f>IF(P219="","",P219/E219)</f>
         <v/>
       </c>
-      <c r="R219" s="5" t="inlineStr"/>
-      <c r="S219" s="5" t="inlineStr"/>
+      <c r="R219" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Мегастрой</t>
+        </is>
+      </c>
+      <c r="S219" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T219" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U219" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U219" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/mezhflantcevyi/odnostvorchatyi/megastroy/19ch21br/dn80</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="34" customHeight="1">
       <c r="A220" s="5" t="inlineStr">
@@ -19943,12 +21055,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K220" s="19" t="n"/>
+      <c r="K220" s="7" t="n">
+        <v>10936.08</v>
+      </c>
       <c r="L220" s="15">
         <f>IF(K220="","",K220*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M220" s="6" t="n"/>
+      <c r="M220" s="6" t="n">
+        <v>5</v>
+      </c>
       <c r="N220" s="15">
         <f>IF(K220="","",L220*E220)</f>
         <v/>
@@ -19965,14 +21081,26 @@
         <f>IF(P220="","",P220/E220)</f>
         <v/>
       </c>
-      <c r="R220" s="5" t="inlineStr"/>
-      <c r="S220" s="5" t="inlineStr"/>
+      <c r="R220" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд АДЛ Гранлок</t>
+        </is>
+      </c>
+      <c r="S220" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T220" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U220" s="5" t="inlineStr"/>
+          <t>analog: АДЛ Гранлок CV16 вместо DENDOR 010C · не провер</t>
+        </is>
+      </c>
+      <c r="U220" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/mezhflantcevyi/dvukhstvorchatyi/granlok/cv16/dn100</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="34" customHeight="1">
       <c r="A221" s="5" t="inlineStr">
@@ -20017,12 +21145,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K221" s="19" t="n"/>
+      <c r="K221" s="7" t="n">
+        <v>12109.11</v>
+      </c>
       <c r="L221" s="15">
         <f>IF(K221="","",K221*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M221" s="6" t="n"/>
+      <c r="M221" s="6" t="n">
+        <v>9</v>
+      </c>
       <c r="N221" s="15">
         <f>IF(K221="","",L221*E221)</f>
         <v/>
@@ -20039,14 +21171,26 @@
         <f>IF(P221="","",P221/E221)</f>
         <v/>
       </c>
-      <c r="R221" s="5" t="inlineStr"/>
-      <c r="S221" s="5" t="inlineStr"/>
+      <c r="R221" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд АДЛ Гранлок</t>
+        </is>
+      </c>
+      <c r="S221" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T221" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U221" s="5" t="inlineStr"/>
+          <t>analog: АДЛ Гранлок CV16 вместо DENDOR 010C · не провер</t>
+        </is>
+      </c>
+      <c r="U221" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/mezhflantcevyi/dvukhstvorchatyi/granlok/cv16/dn150</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="34" customHeight="1">
       <c r="A222" s="5" t="inlineStr">
@@ -20091,12 +21235,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K222" s="19" t="n"/>
+      <c r="K222" s="7" t="n">
+        <v>29968.69</v>
+      </c>
       <c r="L222" s="15">
         <f>IF(K222="","",K222*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M222" s="6" t="n"/>
+      <c r="M222" s="6" t="n">
+        <v>16</v>
+      </c>
       <c r="N222" s="15">
         <f>IF(K222="","",L222*E222)</f>
         <v/>
@@ -20113,14 +21261,26 @@
         <f>IF(P222="","",P222/E222)</f>
         <v/>
       </c>
-      <c r="R222" s="5" t="inlineStr"/>
-      <c r="S222" s="5" t="inlineStr"/>
+      <c r="R222" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд АДЛ Гранлок</t>
+        </is>
+      </c>
+      <c r="S222" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T222" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U222" s="5" t="inlineStr"/>
+          <t>analog: АДЛ Гранлок CV16 вместо DENDOR 010C · не провер</t>
+        </is>
+      </c>
+      <c r="U222" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-obratnyi/mezhflantcevyi/dvukhstvorchatyi/granlok/cv16/dn200</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="34" customHeight="1">
       <c r="A223" s="5" t="inlineStr">
@@ -20167,12 +21327,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K223" s="19" t="n"/>
+      <c r="K223" s="7" t="n">
+        <v>9000</v>
+      </c>
       <c r="L223" s="15">
         <f>IF(K223="","",K223*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M223" s="6" t="n"/>
+      <c r="M223" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="N223" s="15">
         <f>IF(K223="","",L223*E223)</f>
         <v/>
@@ -20189,14 +21353,26 @@
         <f>IF(P223="","",P223/E223)</f>
         <v/>
       </c>
-      <c r="R223" s="5" t="inlineStr"/>
-      <c r="S223" s="5" t="inlineStr"/>
+      <c r="R223" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Газовик»/НовГазТех</t>
+        </is>
+      </c>
+      <c r="S223" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка по соседнему типоразмеру/аналогу (источ</t>
+        </is>
+      </c>
       <c r="T223" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U223" s="5" t="inlineStr"/>
+          <t>exact (марка), цена оценочная · не проверено</t>
+        </is>
+      </c>
+      <c r="U223" s="5" t="inlineStr">
+        <is>
+          <t>https://newgaztech.ru/catalog/plant/product/id/143</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="34" customHeight="1">
       <c r="A224" s="5" t="inlineStr">
@@ -20241,12 +21417,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K224" s="19" t="n"/>
+      <c r="K224" s="7" t="n">
+        <v>18000</v>
+      </c>
       <c r="L224" s="15">
         <f>IF(K224="","",K224*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M224" s="6" t="n"/>
+      <c r="M224" s="6" t="n">
+        <v>6</v>
+      </c>
       <c r="N224" s="15">
         <f>IF(K224="","",L224*E224)</f>
         <v/>
@@ -20263,14 +21443,26 @@
         <f>IF(P224="","",P224/E224)</f>
         <v/>
       </c>
-      <c r="R224" s="5" t="inlineStr"/>
-      <c r="S224" s="5" t="inlineStr"/>
+      <c r="R224" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру/Авангард</t>
+        </is>
+      </c>
+      <c r="S224" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка по соседнему типоразмеру/аналогу (источ</t>
+        </is>
+      </c>
       <c r="T224" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U224" s="5" t="inlineStr"/>
+          <t>exact (марка), оценка по 17с28нж Ду25 · не проверено</t>
+        </is>
+      </c>
+      <c r="U224" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-predokhranitelnyi/flantcevyi/avangard/17s28nzh/dn25-40</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="34" customHeight="1">
       <c r="A225" s="5" t="inlineStr">
@@ -20315,12 +21507,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K225" s="19" t="n"/>
+      <c r="K225" s="7" t="n">
+        <v>22754.83</v>
+      </c>
       <c r="L225" s="15">
         <f>IF(K225="","",K225*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M225" s="6" t="n"/>
+      <c r="M225" s="6" t="n">
+        <v>28</v>
+      </c>
       <c r="N225" s="15">
         <f>IF(K225="","",L225*E225)</f>
         <v/>
@@ -20337,14 +21533,26 @@
         <f>IF(P225="","",P225/E225)</f>
         <v/>
       </c>
-      <c r="R225" s="5" t="inlineStr"/>
-      <c r="S225" s="5" t="inlineStr"/>
+      <c r="R225" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд ВБТА</t>
+        </is>
+      </c>
+      <c r="S225" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T225" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U225" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U225" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-predokhranitelnyi/flantcevyi/vbta/17s28nzh/dn50</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="34" customHeight="1">
       <c r="A226" s="5" t="inlineStr">
@@ -20385,12 +21593,16 @@
         </is>
       </c>
       <c r="J226" s="5" t="inlineStr"/>
-      <c r="K226" s="19" t="n"/>
+      <c r="K226" s="7" t="n">
+        <v>36900.12</v>
+      </c>
       <c r="L226" s="15">
         <f>IF(K226="","",K226*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M226" s="6" t="n"/>
+      <c r="M226" s="6" t="n">
+        <v>35</v>
+      </c>
       <c r="N226" s="15">
         <f>IF(K226="","",L226*E226)</f>
         <v/>
@@ -20407,14 +21619,26 @@
         <f>IF(P226="","",P226/E226)</f>
         <v/>
       </c>
-      <c r="R226" s="5" t="inlineStr"/>
-      <c r="S226" s="5" t="inlineStr"/>
+      <c r="R226" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд ВБТА</t>
+        </is>
+      </c>
+      <c r="S226" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T226" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U226" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U226" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-predokhranitelnyi/flantcevyi/vbta/17s6nzh/dn50</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="34" customHeight="1">
       <c r="A227" s="5" t="inlineStr">
@@ -20455,12 +21679,16 @@
         </is>
       </c>
       <c r="J227" s="5" t="inlineStr"/>
-      <c r="K227" s="19" t="n"/>
+      <c r="K227" s="7" t="n">
+        <v>54119.81</v>
+      </c>
       <c r="L227" s="15">
         <f>IF(K227="","",K227*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M227" s="6" t="n"/>
+      <c r="M227" s="6" t="n">
+        <v>60</v>
+      </c>
       <c r="N227" s="15">
         <f>IF(K227="","",L227*E227)</f>
         <v/>
@@ -20477,14 +21705,26 @@
         <f>IF(P227="","",P227/E227)</f>
         <v/>
       </c>
-      <c r="R227" s="5" t="inlineStr"/>
-      <c r="S227" s="5" t="inlineStr"/>
+      <c r="R227" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд ВБТА</t>
+        </is>
+      </c>
+      <c r="S227" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T227" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U227" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U227" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-predokhranitelnyi/flantcevyi/vbta/17s6nzh/dn80</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="34" customHeight="1">
       <c r="A228" s="5" t="inlineStr">
@@ -20525,12 +21765,16 @@
         </is>
       </c>
       <c r="J228" s="5" t="inlineStr"/>
-      <c r="K228" s="19" t="n"/>
+      <c r="K228" s="7" t="n">
+        <v>8500</v>
+      </c>
       <c r="L228" s="15">
         <f>IF(K228="","",K228*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M228" s="6" t="n"/>
+      <c r="M228" s="6" t="n">
+        <v>7.5</v>
+      </c>
       <c r="N228" s="15">
         <f>IF(K228="","",L228*E228)</f>
         <v/>
@@ -20547,11 +21791,19 @@
         <f>IF(P228="","",P228/E228)</f>
         <v/>
       </c>
-      <c r="R228" s="5" t="inlineStr"/>
-      <c r="S228" s="5" t="inlineStr"/>
+      <c r="R228" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру</t>
+        </is>
+      </c>
+      <c r="S228" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка, без прямого прайса</t>
+        </is>
+      </c>
       <c r="T228" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
+          <t>analog: 15с22нж Ду32 Ру40 (перекрывает Ру25) · не прове</t>
         </is>
       </c>
       <c r="U228" s="5" t="inlineStr"/>
@@ -20685,12 +21937,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K230" s="19" t="n"/>
+      <c r="K230" s="7" t="n">
+        <v>496.54</v>
+      </c>
       <c r="L230" s="15">
         <f>IF(K230="","",K230*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M230" s="6" t="n"/>
+      <c r="M230" s="6" t="n">
+        <v>0.35</v>
+      </c>
       <c r="N230" s="15">
         <f>IF(K230="","",L230*E230)</f>
         <v/>
@@ -20707,14 +21963,26 @@
         <f>IF(P230="","",P230/E230)</f>
         <v/>
       </c>
-      <c r="R230" s="5" t="inlineStr"/>
-      <c r="S230" s="5" t="inlineStr"/>
+      <c r="R230" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Цветлит</t>
+        </is>
+      </c>
+      <c r="S230" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T230" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U230" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U230" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/latun/shturval/tsvetlit/15b1p/dn15</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="34" customHeight="1">
       <c r="A231" s="5" t="inlineStr">
@@ -20759,12 +22027,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K231" s="19" t="n"/>
+      <c r="K231" s="7" t="n">
+        <v>653.3099999999999</v>
+      </c>
       <c r="L231" s="15">
         <f>IF(K231="","",K231*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M231" s="6" t="n"/>
+      <c r="M231" s="6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="N231" s="15">
         <f>IF(K231="","",L231*E231)</f>
         <v/>
@@ -20781,14 +22053,26 @@
         <f>IF(P231="","",P231/E231)</f>
         <v/>
       </c>
-      <c r="R231" s="5" t="inlineStr"/>
-      <c r="S231" s="5" t="inlineStr"/>
+      <c r="R231" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Цветлит</t>
+        </is>
+      </c>
+      <c r="S231" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T231" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U231" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U231" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/latun/shturval/tsvetlit/15b1p/dn20</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="34" customHeight="1">
       <c r="A232" s="5" t="inlineStr">
@@ -20833,12 +22117,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K232" s="19" t="n"/>
+      <c r="K232" s="7" t="n">
+        <v>923.54</v>
+      </c>
       <c r="L232" s="15">
         <f>IF(K232="","",K232*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M232" s="6" t="n"/>
+      <c r="M232" s="6" t="n">
+        <v>0.8</v>
+      </c>
       <c r="N232" s="15">
         <f>IF(K232="","",L232*E232)</f>
         <v/>
@@ -20855,14 +22143,26 @@
         <f>IF(P232="","",P232/E232)</f>
         <v/>
       </c>
-      <c r="R232" s="5" t="inlineStr"/>
-      <c r="S232" s="5" t="inlineStr"/>
+      <c r="R232" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Цветлит</t>
+        </is>
+      </c>
+      <c r="S232" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T232" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U232" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U232" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/latun/shturval/tsvetlit/15b1n-vr-vr/dn25</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="34" customHeight="1">
       <c r="A233" s="5" t="inlineStr">
@@ -20907,12 +22207,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K233" s="19" t="n"/>
+      <c r="K233" s="7" t="n">
+        <v>6000</v>
+      </c>
       <c r="L233" s="15">
         <f>IF(K233="","",K233*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M233" s="6" t="n"/>
+      <c r="M233" s="6" t="n">
+        <v>5</v>
+      </c>
       <c r="N233" s="15">
         <f>IF(K233="","",L233*E233)</f>
         <v/>
@@ -20929,14 +22233,26 @@
         <f>IF(P233="","",P233/E233)</f>
         <v/>
       </c>
-      <c r="R233" s="5" t="inlineStr"/>
-      <c r="S233" s="5" t="inlineStr"/>
+      <c r="R233" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру</t>
+        </is>
+      </c>
+      <c r="S233" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка по соседнему типоразмеру/аналогу (источ</t>
+        </is>
+      </c>
       <c r="T233" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U233" s="5" t="inlineStr"/>
+          <t>exact (марка), оценка · не проверено</t>
+        </is>
+      </c>
+      <c r="U233" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/chugun/shturval/luidor/15kch16p1/dn32</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="34" customHeight="1">
       <c r="A234" s="5" t="inlineStr">
@@ -20981,12 +22297,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K234" s="19" t="n"/>
+      <c r="K234" s="7" t="n">
+        <v>5996.91</v>
+      </c>
       <c r="L234" s="15">
         <f>IF(K234="","",K234*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M234" s="6" t="n"/>
+      <c r="M234" s="6" t="n">
+        <v>7.5</v>
+      </c>
       <c r="N234" s="15">
         <f>IF(K234="","",L234*E234)</f>
         <v/>
@@ -21003,14 +22323,26 @@
         <f>IF(P234="","",P234/E234)</f>
         <v/>
       </c>
-      <c r="R234" s="5" t="inlineStr"/>
-      <c r="S234" s="5" t="inlineStr"/>
+      <c r="R234" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд луидор</t>
+        </is>
+      </c>
+      <c r="S234" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T234" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U234" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U234" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/chugun/shturval/luidor/15kch16p1/dn32</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="34" customHeight="1">
       <c r="A235" s="5" t="inlineStr">
@@ -21055,12 +22387,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K235" s="19" t="n"/>
+      <c r="K235" s="7" t="n">
+        <v>6700.85</v>
+      </c>
       <c r="L235" s="15">
         <f>IF(K235="","",K235*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M235" s="6" t="n"/>
+      <c r="M235" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="N235" s="15">
         <f>IF(K235="","",L235*E235)</f>
         <v/>
@@ -21077,14 +22413,26 @@
         <f>IF(P235="","",P235/E235)</f>
         <v/>
       </c>
-      <c r="R235" s="5" t="inlineStr"/>
-      <c r="S235" s="5" t="inlineStr"/>
+      <c r="R235" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд луидор</t>
+        </is>
+      </c>
+      <c r="S235" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T235" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U235" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U235" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/chugun/shturval/luidor/15kch16p1/dn40</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="34" customHeight="1">
       <c r="A236" s="5" t="inlineStr">
@@ -21129,12 +22477,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K236" s="19" t="n"/>
+      <c r="K236" s="7" t="n">
+        <v>8464.969999999999</v>
+      </c>
       <c r="L236" s="15">
         <f>IF(K236="","",K236*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M236" s="6" t="n"/>
+      <c r="M236" s="6" t="n">
+        <v>14</v>
+      </c>
       <c r="N236" s="15">
         <f>IF(K236="","",L236*E236)</f>
         <v/>
@@ -21151,14 +22503,26 @@
         <f>IF(P236="","",P236/E236)</f>
         <v/>
       </c>
-      <c r="R236" s="5" t="inlineStr"/>
-      <c r="S236" s="5" t="inlineStr"/>
+      <c r="R236" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд луидор</t>
+        </is>
+      </c>
+      <c r="S236" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T236" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U236" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U236" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/chugun/shturval/luidor/15kch16p1/dn50</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="34" customHeight="1">
       <c r="A237" s="5" t="inlineStr">
@@ -21203,12 +22567,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K237" s="19" t="n"/>
+      <c r="K237" s="7" t="n">
+        <v>1190</v>
+      </c>
       <c r="L237" s="15">
         <f>IF(K237="","",K237*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M237" s="6" t="n"/>
+      <c r="M237" s="6" t="n">
+        <v>5</v>
+      </c>
       <c r="N237" s="15">
         <f>IF(K237="","",L237*E237)</f>
         <v/>
@@ -21225,14 +22593,26 @@
         <f>IF(P237="","",P237/E237)</f>
         <v/>
       </c>
-      <c r="R237" s="5" t="inlineStr"/>
-      <c r="S237" s="5" t="inlineStr"/>
+      <c r="R237" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру</t>
+        </is>
+      </c>
+      <c r="S237" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка по соседнему типоразмеру/аналогу (источ</t>
+        </is>
+      </c>
       <c r="T237" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U237" s="5" t="inlineStr"/>
+          <t>exact (марка), оценка рос. исполнения · не проверено</t>
+        </is>
+      </c>
+      <c r="U237" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/chugun/shturval/kitai/15kch19p1/dn25</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="34" customHeight="1">
       <c r="A238" s="5" t="inlineStr">
@@ -21277,12 +22657,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K238" s="19" t="n"/>
+      <c r="K238" s="7" t="n">
+        <v>2810</v>
+      </c>
       <c r="L238" s="15">
         <f>IF(K238="","",K238*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M238" s="6" t="n"/>
+      <c r="M238" s="6" t="n">
+        <v>14</v>
+      </c>
       <c r="N238" s="15">
         <f>IF(K238="","",L238*E238)</f>
         <v/>
@@ -21299,14 +22683,26 @@
         <f>IF(P238="","",P238/E238)</f>
         <v/>
       </c>
-      <c r="R238" s="5" t="inlineStr"/>
-      <c r="S238" s="5" t="inlineStr"/>
+      <c r="R238" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру</t>
+        </is>
+      </c>
+      <c r="S238" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка по соседнему типоразмеру/аналогу (источ</t>
+        </is>
+      </c>
       <c r="T238" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U238" s="5" t="inlineStr"/>
+          <t>exact (марка), оценка рос. исполнения · не проверено</t>
+        </is>
+      </c>
+      <c r="U238" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/chugun/shturval/kitai/15kch19p1/dn50</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="34" customHeight="1">
       <c r="A239" s="5" t="inlineStr">
@@ -21351,12 +22747,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K239" s="19" t="n"/>
+      <c r="K239" s="7" t="n">
+        <v>21808.11</v>
+      </c>
       <c r="L239" s="15">
         <f>IF(K239="","",K239*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M239" s="6" t="n"/>
+      <c r="M239" s="6" t="n">
+        <v>27</v>
+      </c>
       <c r="N239" s="15">
         <f>IF(K239="","",L239*E239)</f>
         <v/>
@@ -21373,14 +22773,26 @@
         <f>IF(P239="","",P239/E239)</f>
         <v/>
       </c>
-      <c r="R239" s="5" t="inlineStr"/>
-      <c r="S239" s="5" t="inlineStr"/>
+      <c r="R239" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд ТехГидроМаш</t>
+        </is>
+      </c>
+      <c r="S239" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T239" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U239" s="5" t="inlineStr"/>
+          <t>analog: 08Х18Н10 (≈AISI 304) · не проверено</t>
+        </is>
+      </c>
+      <c r="U239" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/stalnoi/shturval/tekhgidromash/15nzh65nzh/dn80</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="34" customHeight="1">
       <c r="A240" s="5" t="inlineStr">
@@ -21425,12 +22837,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K240" s="19" t="n"/>
+      <c r="K240" s="7" t="n">
+        <v>27871.51</v>
+      </c>
       <c r="L240" s="15">
         <f>IF(K240="","",K240*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M240" s="6" t="n"/>
+      <c r="M240" s="6" t="n">
+        <v>40</v>
+      </c>
       <c r="N240" s="15">
         <f>IF(K240="","",L240*E240)</f>
         <v/>
@@ -21447,14 +22863,26 @@
         <f>IF(P240="","",P240/E240)</f>
         <v/>
       </c>
-      <c r="R240" s="5" t="inlineStr"/>
-      <c r="S240" s="5" t="inlineStr"/>
+      <c r="R240" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд ТехГидроМаш</t>
+        </is>
+      </c>
+      <c r="S240" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T240" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U240" s="5" t="inlineStr"/>
+          <t>analog: 08Х18Н10 (≈AISI 304) · не проверено</t>
+        </is>
+      </c>
+      <c r="U240" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/stalnoi/shturval/tekhgidromash/15nzh65nzh/dn100</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="34" customHeight="1">
       <c r="A241" s="5" t="inlineStr">
@@ -21499,12 +22927,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K241" s="19" t="n"/>
+      <c r="K241" s="7" t="n">
+        <v>8512.549999999999</v>
+      </c>
       <c r="L241" s="15">
         <f>IF(K241="","",K241*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M241" s="6" t="n"/>
+      <c r="M241" s="6" t="n">
+        <v>7.5</v>
+      </c>
       <c r="N241" s="15">
         <f>IF(K241="","",L241*E241)</f>
         <v/>
@@ -21521,14 +22953,26 @@
         <f>IF(P241="","",P241/E241)</f>
         <v/>
       </c>
-      <c r="R241" s="5" t="inlineStr"/>
-      <c r="S241" s="5" t="inlineStr"/>
+      <c r="R241" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд ТехГидроМаш</t>
+        </is>
+      </c>
+      <c r="S241" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T241" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U241" s="5" t="inlineStr"/>
+          <t>analog: 08Х18Н10 (≈AISI 304) · не проверено</t>
+        </is>
+      </c>
+      <c r="U241" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/stalnoi/shturval/tekhgidromash/15nzh65nzh/dn32</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="34" customHeight="1">
       <c r="A242" s="5" t="inlineStr">
@@ -21573,12 +23017,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K242" s="19" t="n"/>
+      <c r="K242" s="7" t="n">
+        <v>7500</v>
+      </c>
       <c r="L242" s="15">
         <f>IF(K242="","",K242*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M242" s="6" t="n"/>
+      <c r="M242" s="6" t="n">
+        <v>7.5</v>
+      </c>
       <c r="N242" s="15">
         <f>IF(K242="","",L242*E242)</f>
         <v/>
@@ -21595,11 +23043,19 @@
         <f>IF(P242="","",P242/E242)</f>
         <v/>
       </c>
-      <c r="R242" s="5" t="inlineStr"/>
-      <c r="S242" s="5" t="inlineStr"/>
+      <c r="R242" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру</t>
+        </is>
+      </c>
+      <c r="S242" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка, без прямого прайса</t>
+        </is>
+      </c>
       <c r="T242" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
+          <t>analog: 15с22нж Ду32 Ру40 · не проверено</t>
         </is>
       </c>
       <c r="U242" s="5" t="inlineStr"/>
@@ -21647,12 +23103,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K243" s="19" t="n"/>
+      <c r="K243" s="7" t="n">
+        <v>19907.96</v>
+      </c>
       <c r="L243" s="15">
         <f>IF(K243="","",K243*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M243" s="6" t="n"/>
+      <c r="M243" s="6" t="n">
+        <v>27</v>
+      </c>
       <c r="N243" s="15">
         <f>IF(K243="","",L243*E243)</f>
         <v/>
@@ -21669,14 +23129,26 @@
         <f>IF(P243="","",P243/E243)</f>
         <v/>
       </c>
-      <c r="R243" s="5" t="inlineStr"/>
-      <c r="S243" s="5" t="inlineStr"/>
+      <c r="R243" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру, «Россия»</t>
+        </is>
+      </c>
+      <c r="S243" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка по соседнему типоразмеру/аналогу (источ</t>
+        </is>
+      </c>
       <c r="T243" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U243" s="5" t="inlineStr"/>
+          <t>analog: 15с22нж Ду80 Ру40 · не проверено</t>
+        </is>
+      </c>
+      <c r="U243" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/stalnoi/shturval/russia/15s22nzh/dn80</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="34" customHeight="1">
       <c r="A244" s="5" t="inlineStr">
@@ -21721,12 +23193,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K244" s="19" t="n"/>
+      <c r="K244" s="7" t="n">
+        <v>25000</v>
+      </c>
       <c r="L244" s="15">
         <f>IF(K244="","",K244*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M244" s="6" t="n"/>
+      <c r="M244" s="6" t="n">
+        <v>40</v>
+      </c>
       <c r="N244" s="15">
         <f>IF(K244="","",L244*E244)</f>
         <v/>
@@ -21743,11 +23219,19 @@
         <f>IF(P244="","",P244/E244)</f>
         <v/>
       </c>
-      <c r="R244" s="5" t="inlineStr"/>
-      <c r="S244" s="5" t="inlineStr"/>
+      <c r="R244" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру</t>
+        </is>
+      </c>
+      <c r="S244" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка, без прямого прайса</t>
+        </is>
+      </c>
       <c r="T244" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
+          <t>analog: 15с22нж/15с18нж Ду100 · не проверено</t>
         </is>
       </c>
       <c r="U244" s="5" t="inlineStr"/>
@@ -21795,12 +23279,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K245" s="19" t="n"/>
+      <c r="K245" s="7" t="n">
+        <v>5500</v>
+      </c>
       <c r="L245" s="15">
         <f>IF(K245="","",K245*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M245" s="6" t="n"/>
+      <c r="M245" s="6" t="n">
+        <v>5</v>
+      </c>
       <c r="N245" s="15">
         <f>IF(K245="","",L245*E245)</f>
         <v/>
@@ -21817,11 +23305,19 @@
         <f>IF(P245="","",P245/E245)</f>
         <v/>
       </c>
-      <c r="R245" s="5" t="inlineStr"/>
-      <c r="S245" s="5" t="inlineStr"/>
+      <c r="R245" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру</t>
+        </is>
+      </c>
+      <c r="S245" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка, без прямого прайса</t>
+        </is>
+      </c>
       <c r="T245" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
+          <t>exact (марка), оценка · не проверено</t>
         </is>
       </c>
       <c r="U245" s="5" t="inlineStr"/>
@@ -21869,12 +23365,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K246" s="19" t="n"/>
+      <c r="K246" s="7" t="n">
+        <v>7500</v>
+      </c>
       <c r="L246" s="15">
         <f>IF(K246="","",K246*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M246" s="6" t="n"/>
+      <c r="M246" s="6" t="n">
+        <v>7.5</v>
+      </c>
       <c r="N246" s="15">
         <f>IF(K246="","",L246*E246)</f>
         <v/>
@@ -21891,11 +23391,19 @@
         <f>IF(P246="","",P246/E246)</f>
         <v/>
       </c>
-      <c r="R246" s="5" t="inlineStr"/>
-      <c r="S246" s="5" t="inlineStr"/>
+      <c r="R246" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру</t>
+        </is>
+      </c>
+      <c r="S246" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка, без прямого прайса</t>
+        </is>
+      </c>
       <c r="T246" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
+          <t>exact (марка), оценка · не проверено</t>
         </is>
       </c>
       <c r="U246" s="5" t="inlineStr"/>
@@ -21943,12 +23451,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K247" s="19" t="n"/>
+      <c r="K247" s="7" t="n">
+        <v>9180.5</v>
+      </c>
       <c r="L247" s="15">
         <f>IF(K247="","",K247*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M247" s="6" t="n"/>
+      <c r="M247" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="N247" s="15">
         <f>IF(K247="","",L247*E247)</f>
         <v/>
@@ -21965,14 +23477,26 @@
         <f>IF(P247="","",P247/E247)</f>
         <v/>
       </c>
-      <c r="R247" s="5" t="inlineStr"/>
-      <c r="S247" s="5" t="inlineStr"/>
+      <c r="R247" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Россия</t>
+        </is>
+      </c>
+      <c r="S247" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T247" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U247" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U247" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/stalnoi/shturval/russia/15s22nzh/dn40</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="34" customHeight="1">
       <c r="A248" s="5" t="inlineStr">
@@ -22017,12 +23541,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K248" s="19" t="n"/>
+      <c r="K248" s="7" t="n">
+        <v>10529.82</v>
+      </c>
       <c r="L248" s="15">
         <f>IF(K248="","",K248*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M248" s="6" t="n"/>
+      <c r="M248" s="6" t="n">
+        <v>14</v>
+      </c>
       <c r="N248" s="15">
         <f>IF(K248="","",L248*E248)</f>
         <v/>
@@ -22039,14 +23567,26 @@
         <f>IF(P248="","",P248/E248)</f>
         <v/>
       </c>
-      <c r="R248" s="5" t="inlineStr"/>
-      <c r="S248" s="5" t="inlineStr"/>
+      <c r="R248" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Россия</t>
+        </is>
+      </c>
+      <c r="S248" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T248" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U248" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U248" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/stalnoi/shturval/russia/15s22nzh/dn50</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="34" customHeight="1">
       <c r="A249" s="5" t="inlineStr">
@@ -22091,12 +23631,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K249" s="19" t="n"/>
+      <c r="K249" s="7" t="n">
+        <v>19907.96</v>
+      </c>
       <c r="L249" s="15">
         <f>IF(K249="","",K249*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M249" s="6" t="n"/>
+      <c r="M249" s="6" t="n">
+        <v>27</v>
+      </c>
       <c r="N249" s="15">
         <f>IF(K249="","",L249*E249)</f>
         <v/>
@@ -22113,14 +23657,26 @@
         <f>IF(P249="","",P249/E249)</f>
         <v/>
       </c>
-      <c r="R249" s="5" t="inlineStr"/>
-      <c r="S249" s="5" t="inlineStr"/>
+      <c r="R249" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд Россия</t>
+        </is>
+      </c>
+      <c r="S249" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T249" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U249" s="5" t="inlineStr"/>
+          <t>exact · не проверено</t>
+        </is>
+      </c>
+      <c r="U249" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/stalnoi/shturval/russia/15s22nzh/dn80</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="34" customHeight="1">
       <c r="A250" s="5" t="inlineStr">
@@ -22165,12 +23721,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K250" s="19" t="n"/>
+      <c r="K250" s="7" t="n">
+        <v>16328.91</v>
+      </c>
       <c r="L250" s="15">
         <f>IF(K250="","",K250*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M250" s="6" t="n"/>
+      <c r="M250" s="6" t="n">
+        <v>40</v>
+      </c>
       <c r="N250" s="15">
         <f>IF(K250="","",L250*E250)</f>
         <v/>
@@ -22187,14 +23747,26 @@
         <f>IF(P250="","",P250/E250)</f>
         <v/>
       </c>
-      <c r="R250" s="5" t="inlineStr"/>
-      <c r="S250" s="5" t="inlineStr"/>
+      <c r="R250" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд ТехГидроМаш</t>
+        </is>
+      </c>
+      <c r="S250" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T250" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U250" s="5" t="inlineStr"/>
+          <t>exact + КОФ (ответные фланцы+крепёж ≈ +3500 ₽ оценка) ·</t>
+        </is>
+      </c>
+      <c r="U250" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/stalnoi/shturval/tekhgidromash/15s65nzh/dn100</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="34" customHeight="1">
       <c r="A251" s="5" t="inlineStr">
@@ -22239,12 +23811,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K251" s="19" t="n"/>
+      <c r="K251" s="7" t="n">
+        <v>3362.61</v>
+      </c>
       <c r="L251" s="15">
         <f>IF(K251="","",K251*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M251" s="6" t="n"/>
+      <c r="M251" s="6" t="n">
+        <v>5</v>
+      </c>
       <c r="N251" s="15">
         <f>IF(K251="","",L251*E251)</f>
         <v/>
@@ -22261,14 +23837,26 @@
         <f>IF(P251="","",P251/E251)</f>
         <v/>
       </c>
-      <c r="R251" s="5" t="inlineStr"/>
-      <c r="S251" s="5" t="inlineStr"/>
+      <c r="R251" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд ТехГидроМаш</t>
+        </is>
+      </c>
+      <c r="S251" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T251" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U251" s="5" t="inlineStr"/>
+          <t xml:space="preserve">exact + КОФ (ответные фланцы+крепёж ≈ +800 ₽ оценка) · </t>
+        </is>
+      </c>
+      <c r="U251" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/stalnoi/shturval/tekhgidromash/15s65nzh/dn25</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="34" customHeight="1">
       <c r="A252" s="5" t="inlineStr">
@@ -22313,12 +23901,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K252" s="19" t="n"/>
+      <c r="K252" s="7" t="n">
+        <v>5349.83</v>
+      </c>
       <c r="L252" s="15">
         <f>IF(K252="","",K252*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M252" s="6" t="n"/>
+      <c r="M252" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="N252" s="15">
         <f>IF(K252="","",L252*E252)</f>
         <v/>
@@ -22335,14 +23927,26 @@
         <f>IF(P252="","",P252/E252)</f>
         <v/>
       </c>
-      <c r="R252" s="5" t="inlineStr"/>
-      <c r="S252" s="5" t="inlineStr"/>
+      <c r="R252" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд ТехГидроМаш</t>
+        </is>
+      </c>
+      <c r="S252" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T252" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U252" s="5" t="inlineStr"/>
+          <t>exact + КОФ (ответные фланцы+крепёж ≈ +1200 ₽ оценка) ·</t>
+        </is>
+      </c>
+      <c r="U252" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/stalnoi/shturval/tekhgidromash/15s65nzh/dn40</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="34" customHeight="1">
       <c r="A253" s="5" t="inlineStr">
@@ -22387,12 +23991,16 @@
           <t>ручной (маховик)</t>
         </is>
       </c>
-      <c r="K253" s="19" t="n"/>
+      <c r="K253" s="7" t="n">
+        <v>6662.43</v>
+      </c>
       <c r="L253" s="15">
         <f>IF(K253="","",K253*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M253" s="6" t="n"/>
+      <c r="M253" s="6" t="n">
+        <v>14</v>
+      </c>
       <c r="N253" s="15">
         <f>IF(K253="","",L253*E253)</f>
         <v/>
@@ -22409,14 +24017,26 @@
         <f>IF(P253="","",P253/E253)</f>
         <v/>
       </c>
-      <c r="R253" s="5" t="inlineStr"/>
-      <c r="S253" s="5" t="inlineStr"/>
+      <c r="R253" s="5" t="inlineStr">
+        <is>
+          <t>ДН.ру (dn.ru), бренд ТехГидроМаш</t>
+        </is>
+      </c>
+      <c r="S253" s="5" t="inlineStr">
+        <is>
+          <t>розница · B: dn.ru — живой магазин ООО «ДН.ру», © 2026,</t>
+        </is>
+      </c>
       <c r="T253" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
-        </is>
-      </c>
-      <c r="U253" s="5" t="inlineStr"/>
+          <t>exact + КОФ (ответные фланцы+крепёж ≈ +1500 ₽ оценка) ·</t>
+        </is>
+      </c>
+      <c r="U253" s="5" t="inlineStr">
+        <is>
+          <t>https://dn.ru/klapan/klapan-zapornyi/2hod/stalnoi/shturval/tekhgidromash/15s65nzh/dn50</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="34" customHeight="1">
       <c r="A254" s="5" t="inlineStr">
@@ -27052,12 +28672,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K305" s="19" t="n"/>
+      <c r="K305" s="7" t="n">
+        <v>45000</v>
+      </c>
       <c r="L305" s="15">
         <f>IF(K305="","",K305*(1-0.1))</f>
         <v/>
       </c>
-      <c r="M305" s="6" t="n"/>
+      <c r="M305" s="6" t="n">
+        <v>2.5</v>
+      </c>
       <c r="N305" s="15">
         <f>IF(K305="","",L305*E305)</f>
         <v/>
@@ -27074,11 +28698,19 @@
         <f>IF(P305="","",P305/E305)</f>
         <v/>
       </c>
-      <c r="R305" s="5" t="inlineStr"/>
-      <c r="S305" s="5" t="inlineStr"/>
+      <c r="R305" s="5" t="inlineStr">
+        <is>
+          <t>дилеры Dungs</t>
+        </is>
+      </c>
+      <c r="S305" s="5" t="inlineStr">
+        <is>
+          <t>оценка · оценка, без прямого прайса</t>
+        </is>
+      </c>
       <c r="T305" s="5" t="inlineStr">
         <is>
-          <t>не проверено</t>
+          <t>exact (марка), цена оценочная · не проверено</t>
         </is>
       </c>
       <c r="U305" s="5" t="inlineStr"/>
@@ -28184,15 +29816,15 @@
       <c r="K318" s="8" t="inlineStr"/>
       <c r="L318" s="8" t="inlineStr"/>
       <c r="M318" s="8" t="inlineStr"/>
-      <c r="N318" s="20">
+      <c r="N318" s="19">
         <f>SUM(N3:N317)</f>
         <v/>
       </c>
-      <c r="O318" s="20">
+      <c r="O318" s="19">
         <f>SUM(O3:O317)</f>
         <v/>
       </c>
-      <c r="P318" s="20">
+      <c r="P318" s="19">
         <f>SUM(P3:P317)</f>
         <v/>
       </c>
@@ -28205,205 +29837,294 @@
   </sheetData>
   <autoFilter ref="A2:U317"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U8" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U9" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U10" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U11" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U12" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U13" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U14" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U15" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U16" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U17" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U19" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U20" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U21" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U22" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U23" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U24" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U25" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U26" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U27" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U28" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U29" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U30" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U31" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U44" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U63" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U64" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U65" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U99" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U100" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U101" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U102" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U103" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U104" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U105" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U106" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U107" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U108" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U109" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U110" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U111" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U112" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U113" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U114" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U115" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U116" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U117" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U118" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U119" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U120" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U121" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U122" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U123" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U124" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U125" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U126" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U127" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U128" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U129" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U130" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U132" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U133" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U134" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U135" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U136" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U137" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U138" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U139" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U140" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U141" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U142" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U143" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U144" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U145" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U146" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U147" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U148" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U149" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U150" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U151" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U152" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U153" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U154" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U155" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U156" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U157" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U158" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U159" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U160" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U161" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U162" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U163" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U164" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U165" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U166" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U167" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U168" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U169" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U170" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U171" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U172" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U173" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U174" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U175" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U176" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U179" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U180" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U181" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U182" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U183" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U184" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U185" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U186" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U187" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U188" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U189" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U190" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U191" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U192" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U193" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U197" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U198" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U199" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U200" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U201" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U202" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U203" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U204" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U205" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U206" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U207" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U208" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U209" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U210" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U211" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U212" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U213" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U254" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U255" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U256" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U257" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U258" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U259" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U260" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U261" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U262" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U264" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U265" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U266" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U267" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U268" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U269" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U270" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U271" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U272" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U273" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U274" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U275" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U276" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U277" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U278" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U279" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U280" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U281" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U282" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U283" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U284" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U285" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U286" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U287" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U288" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U289" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U290" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U291" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U292" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U293" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U294" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U295" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U296" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U297" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U298" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U299" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U300" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U301" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U302" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U303" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U304" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U307" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U308" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U309" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U310" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U311" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U312" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U313" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U314" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U315" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U316" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U317" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U38" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U39" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U43" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U44" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U45" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U46" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U47" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U48" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U49" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U50" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U51" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U52" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U53" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U54" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U55" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U56" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U57" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U58" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U59" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U60" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U61" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U62" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U63" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U64" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U65" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U66" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U67" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U68" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U69" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U79" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U80" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U81" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U82" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U83" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U84" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U85" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U86" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U87" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U88" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U89" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U90" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U91" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U92" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U93" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U94" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U99" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U100" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U101" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U102" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U103" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U104" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U105" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U106" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U107" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U108" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U109" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U110" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U111" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U112" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U113" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U114" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U115" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U116" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U117" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U118" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U119" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U120" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U121" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U122" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U123" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U124" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U125" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U126" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U127" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U128" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U129" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U130" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U132" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U133" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U134" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U135" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U136" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U137" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U138" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U139" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U140" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U141" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U142" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U143" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U144" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U145" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U146" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U147" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U148" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U149" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U150" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U151" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U152" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U153" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U154" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U155" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U156" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U157" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U158" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U159" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U160" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U161" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U162" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U163" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U164" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U165" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U166" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U167" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U168" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U169" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U170" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U171" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U172" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U173" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U174" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U175" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U176" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U179" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U180" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U181" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U182" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U183" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U184" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U185" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U186" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U187" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U188" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U189" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U190" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U191" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U192" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U193" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U196" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U197" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U198" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U199" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U200" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U201" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U202" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U203" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U204" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U205" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U206" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U207" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U208" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U209" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U210" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U211" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U212" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U213" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U214" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U215" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U216" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U217" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U218" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U219" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U220" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U221" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U222" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U223" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U224" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U225" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U226" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U227" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U230" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U231" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U232" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U233" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U234" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U235" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U236" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U237" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U238" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U239" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U240" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U241" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U243" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U247" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U248" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U249" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U250" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U251" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U252" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U253" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U254" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U255" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U256" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U257" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U258" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U259" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U260" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U261" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U262" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U264" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U265" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U266" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U267" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U268" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U269" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U270" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U271" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U272" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U273" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U274" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U275" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U276" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U277" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U278" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U279" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U280" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U281" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U282" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U283" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U284" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U285" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U286" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U287" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U288" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U289" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U290" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U291" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U292" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U293" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U294" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U295" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U296" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U297" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U298" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U299" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U300" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U301" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U302" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U303" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U304" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U307" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U308" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U309" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U310" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U311" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U312" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U313" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U314" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U315" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U316" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U317" r:id="rId288"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
